--- a/Call_Module/Calls_Module_Test_Cases.xlsx
+++ b/Call_Module/Calls_Module_Test_Cases.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2052,13 +2052,689 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Call</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on a conversation</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verify initiating an audio call</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a one-on-one conversation.
+2. Click the audio call (phone) icon in header.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Audio call should initiate. Calling screen should appear with user name, avatar, and call controls.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call ringing state</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Initiate an audio call to another user.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Ringing state should display with 'Calling...' or ringing indicator. Ring tone should play.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call connected state</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Initiate audio call.
+2. Other user accepts.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Call should connect. Timer should start. Audio should be active both ways.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call mute/unmute</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. During an active audio call.
+2. Click mute button.
+3. Click unmute.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Mute should silence outgoing audio. Unmute should restore it. Icon should toggle.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call speaker toggle</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. During an active audio call.
+2. Click speaker button.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Audio should switch between earpiece and speaker. Icon should toggle.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify ending an audio call</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. During an active audio call.
+2. Click end call (red) button.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Call should end. Both users should return to chat. Call duration should log.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call in group</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a group conversation.
+2. Initiate an audio call.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Group audio call should initiate. All members should receive call notification.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Call</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call when user is offline</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to audio call a user who is offline.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Call should ring and eventually show 'User unavailable' or similar message.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call fails without network</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to initiate an audio call.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display indicating no network connection.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on an active call</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call drops on network loss</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Be on an active audio call.
+2. Disconnect network.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Call should drop with reconnecting attempt or error message.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Verify Incoming Call</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and app is open</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming audio call notification</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Another user initiates an audio call to you.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming video call notification</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Another user initiates a video call to you.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify accepting an incoming audio call</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming audio call.
+2. Click accept/answer button.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Audio call should connect. Call screen should show with active call controls.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Verify accepting an incoming video call</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming video call.
+2. Click accept/answer button.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Video call should connect with both video feeds visible.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Verify rejecting an incoming call</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming call.
+2. Click reject/decline button.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Call should be rejected. Caller should see 'Call declined' or similar. Call logged as missed.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming call when app is in background</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Minimize the app.
+2. Another user calls you.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Push notification or system call UI should appear allowing accept/reject.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming group call notification</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. A group member initiates a group call.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Incoming group call notification should appear with group name and accept/reject options.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Verify missed call when not answered</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming call.
+2. Do not answer until it times out.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Call should be logged as 'Missed' in call logs. Missed call notification should appear.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Verify Incoming Call</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with Do Not Disturb enabled</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming call behavior with DND</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Enable Do Not Disturb.
+2. Receive an incoming call.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Call should be silenced or blocked based on DND settings. Call logged as missed.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and already on a call</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming call while on another call</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Be on an active call.
+2. Receive another incoming call.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Second call notification should appear with option to accept (end current) or reject.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="B25:B30"/>
     <mergeCell ref="C15:C20"/>
+    <mergeCell ref="B21:B24"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B21:B24"/>
     <mergeCell ref="D21:D24"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="D36:D37"/>

--- a/Call_Module/Calls_Module_Test_Cases.xlsx
+++ b/Call_Module/Calls_Module_Test_Cases.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2725,6 +2725,965 @@
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Call Module with Message List</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Verify call log entry created after completing a call</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Make a call.
+2. End call.
+3. Check call logs.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>New call log entry should appear with correct caller, duration, and timestamp.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Call Module with Conversation List</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Verify call creates/updates conversation in conversation list</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Make a call to a user.
+2. Check conversation list.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Conversation with that user should show call activity (e.g., 'Voice call - 2:30').</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Call Module with Notifications</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Verify missed call notification</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Call User B.
+2. User B doesn't answer.
+3. Check User B's notifications.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>User B should receive a missed call notification with caller info.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Regression: Call Module</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Verify call logs persist after app restart</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Make several calls.
+2. Close and reopen app.
+3. Check call logs.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>All call logs should be intact with correct details.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Verify call functionality after network reconnection</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Lose network.
+2. Reconnect.
+3. Make a call.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Call should work normally after network reconnection.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Verify call logs after clearing call history</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Clear call history.
+2. Make a new call.
+3. Check logs.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Only the new call should appear. Old logs should be cleared.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Security: Call Module</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Verify call cannot be initiated to blocked user</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. Block a user.
+2. Try to call that user.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Call should be blocked with appropriate message.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Verify call audio/video stream is encrypted</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Initiate a call.
+2. Inspect network traffic.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Media streams should be encrypted (SRTP/DTLS). No plain media in transit.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Verify call logs only show user's own calls</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as User A.
+2. Check call logs.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Only calls involving User A should display. No other users' call history visible.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>User is not logged in</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Verify call module not accessible without authentication</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to access call logs without logging in.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Should redirect to login. No call data exposed.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Call Module</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Verify call behavior when switching between WiFi and cellular</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a call on WiFi.
+2. Switch to cellular mid-call.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Call should continue with brief interruption or seamless handoff.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Verify call with very long duration (1+ hour)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Maintain a call for 1+ hour.
+2. End call.
+3. Check log.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Call should remain stable. Log should show correct duration.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Verify multiple simultaneous group calls</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1. Have two different groups initiate calls at the same time.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>User should receive both notifications. Can join one at a time.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Verify call log with 1000+ entries</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Have 1000+ call log entries.
+2. Open call logs.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Logs should load with pagination. No performance issues.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Verify call when microphone permission is denied</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1. Deny microphone permission.
+2. Try to make an audio call.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Should show permission request or error message. Call should not proceed without mic.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Verify video call when camera permission is denied</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1. Deny camera permission.
+2. Try to make a video call.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Should show permission request or fall back to audio-only call.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Boundary: Call Module</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Verify call log with exactly 0 entries</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1. Login with new account.
+2. Open call logs.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display with appropriate message.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Verify call log with exactly 1 entry</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>1. Make one call.
+2. Open call logs.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Single call log should display correctly with all details.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Verify call duration of 0 seconds (immediate hang up)</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>1. Call and immediately hang up.
+2. Check call log.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Call should log as missed or with 0:00 duration.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Verify group call with maximum participants</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a group call with maximum allowed participants.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>All participants should connect. Audio/video should work for all.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Call Types</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Verify one-on-one audio call</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1. Make an audio call to a single user.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Audio call should connect with clear audio both ways.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Verify one-on-one video call</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>1. Make a video call to a single user.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Video call should connect with video and audio both ways.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Verify group audio call</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1. Make an audio call in a group.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>All participants should hear each other.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Verify group video call</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Make a video call in a group.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>All participants should see and hear each other. Grid/tile layout should adjust.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Call Log Types</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Verify outgoing call log display</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. Make an outgoing call.
+2. Check call log.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Should show outgoing call icon, contact name, duration, and timestamp.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming call log display</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive and answer an incoming call.
+2. Check call log.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Should show incoming call icon, caller name, duration, and timestamp.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Verify missed call log display</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>1. Miss an incoming call.
+2. Check call log.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Should show missed call icon (red), caller name, and timestamp. No duration.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Verify rejected call log display</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. Reject an incoming call.
+2. Check call log.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Should show rejected/missed call entry with appropriate icon.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>

--- a/Call_Module/Calls_Module_Test_Cases.xlsx
+++ b/Call_Module/Calls_Module_Test_Cases.xlsx
@@ -7,7 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Calls Module Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,6 +33,8 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -38,12 +46,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,32 +65,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,11 +77,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,23 +439,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
@@ -521,7 +504,7 @@
           <t>CALLS_001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -565,9 +548,9 @@
           <t>CALLS_002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify caller name display</t>
@@ -596,9 +579,9 @@
           <t>CALLS_003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify caller profile picture display</t>
@@ -627,9 +610,9 @@
           <t>CALLS_004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify call timestamp display</t>
@@ -658,9 +641,9 @@
           <t>CALLS_005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify outgoing call indicator (green arrow)</t>
@@ -690,9 +673,9 @@
           <t>CALLS_006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify missed call indicator (red)</t>
@@ -722,9 +705,9 @@
           <t>CALLS_007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify call icon on right side</t>
@@ -753,9 +736,9 @@
           <t>CALLS_008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify multiple calls from same user display separately</t>
@@ -784,9 +767,9 @@
           <t>CALLS_009</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify selected call log highlight</t>
@@ -816,7 +799,7 @@
           <t>CALLS_010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -859,8 +842,8 @@
           <t>CALLS_011</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>User is logged in, caller has very long name</t>
@@ -983,7 +966,7 @@
           <t>CALLS_014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1027,9 +1010,9 @@
           <t>CALLS_015</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify caller info in Call Details</t>
@@ -1059,9 +1042,9 @@
           <t>CALLS_016</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify call type display (Missed Call)</t>
@@ -1091,9 +1074,9 @@
           <t>CALLS_017</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify call duration display</t>
@@ -1123,9 +1106,9 @@
           <t>CALLS_018</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Verify voice call button in Call Details</t>
@@ -1155,9 +1138,9 @@
           <t>CALLS_019</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verify video call button in Call Details</t>
@@ -1187,7 +1170,7 @@
           <t>CALLS_020</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1231,9 +1214,9 @@
           <t>CALLS_021</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify Recording tab display</t>
@@ -1263,9 +1246,9 @@
           <t>CALLS_022</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify History tab display</t>
@@ -1295,9 +1278,9 @@
           <t>CALLS_023</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Verify tab switching functionality</t>
@@ -1327,7 +1310,7 @@
           <t>CALLS_024</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1371,9 +1354,9 @@
           <t>CALLS_025</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Verify participant profile picture</t>
@@ -1403,9 +1386,9 @@
           <t>CALLS_026</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Verify participant name display</t>
@@ -1435,9 +1418,9 @@
           <t>CALLS_027</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Verify participant join timestamp</t>
@@ -1467,9 +1450,9 @@
           <t>CALLS_028</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Verify participant call duration</t>
@@ -1499,9 +1482,9 @@
           <t>CALLS_029</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Verify multiple participants display</t>
@@ -1751,7 +1734,7 @@
           <t>CALLS_035</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1795,9 +1778,9 @@
           <t>CALLS_036</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Verify video call initiation from details</t>
@@ -1827,7 +1810,7 @@
           <t>CALLS_037</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1871,9 +1854,9 @@
           <t>CALLS_038</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Verify Calls module on mobile device</t>
@@ -1903,7 +1886,7 @@
           <t>CALLS_039</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1946,9 +1929,9 @@
           <t>CALLS_040</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
@@ -1978,7 +1961,7 @@
           <t>CALLS_041</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2022,8 +2005,8 @@
           <t>CALLS_042</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
@@ -2101,9 +2084,9 @@
           <t>CALLS_044</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Verify audio call ringing state</t>
@@ -2131,9 +2114,9 @@
           <t>CALLS_045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Verify audio call connected state</t>
@@ -2162,9 +2145,9 @@
           <t>CALLS_046</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr"/>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Verify audio call mute/unmute</t>
@@ -2194,9 +2177,9 @@
           <t>CALLS_047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Verify audio call speaker toggle</t>
@@ -2225,9 +2208,9 @@
           <t>CALLS_048</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr"/>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Verify ending an audio call</t>
@@ -2256,9 +2239,9 @@
           <t>CALLS_049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr"/>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Verify audio call in group</t>
@@ -2329,8 +2312,8 @@
           <t>CALLS_051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr"/>
-      <c r="C52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
@@ -2364,8 +2347,8 @@
           <t>CALLS_052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr"/>
-      <c r="C53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on an active call</t>
@@ -2441,9 +2424,9 @@
           <t>CALLS_054</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Verify incoming video call notification</t>
@@ -2471,9 +2454,9 @@
           <t>CALLS_055</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr"/>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Verify accepting an incoming audio call</t>
@@ -2502,9 +2485,9 @@
           <t>CALLS_056</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr"/>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Verify accepting an incoming video call</t>
@@ -2533,9 +2516,9 @@
           <t>CALLS_057</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Verify rejecting an incoming call</t>
@@ -2564,9 +2547,9 @@
           <t>CALLS_058</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr"/>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Verify incoming call when app is in background</t>
@@ -2595,9 +2578,9 @@
           <t>CALLS_059</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Verify incoming group call notification</t>
@@ -2625,9 +2608,9 @@
           <t>CALLS_060</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr"/>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Verify missed call when not answered</t>
@@ -2699,8 +2682,8 @@
           <t>CALLS_062</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr"/>
-      <c r="C63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t>User is logged in and already on a call</t>
@@ -2728,993 +2711,1368 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CALLS_063</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: Call Module with Message List</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify call log entry created after completing a call</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Make a call.
 2. End call.
 3. Check call logs.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>New call log entry should appear with correct caller, duration, and timestamp.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CALLS_064</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr"/>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Integration: Call Module with Conversation List</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify call creates/updates conversation in conversation list</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Make a call to a user.
 2. Check conversation list.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Conversation with that user should show call activity (e.g., 'Voice call - 2:30').</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CALLS_065</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Integration: Call Module with Notifications</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify missed call notification</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Call User B.
 2. User B doesn't answer.
 3. Check User B's notifications.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>User B should receive a missed call notification with caller info.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CALLS_066</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: Call Module</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify call logs persist after app restart</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Make several calls.
 2. Close and reopen app.
 3. Check call logs.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>All call logs should be intact with correct details.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CALLS_067</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify call functionality after network reconnection</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Lose network.
 2. Reconnect.
 3. Make a call.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Call should work normally after network reconnection.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CALLS_068</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr"/>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify call logs after clearing call history</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Clear call history.
 2. Make a new call.
 3. Check logs.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Only the new call should appear. Old logs should be cleared.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CALLS_069</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: Call Module</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify call cannot be initiated to blocked user</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Block a user.
 2. Try to call that user.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Call should be blocked with appropriate message.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CALLS_070</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr"/>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify call audio/video stream is encrypted</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Initiate a call.
 2. Inspect network traffic.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Media streams should be encrypted (SRTP/DTLS). No plain media in transit.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CALLS_071</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify call logs only show user's own calls</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Login as User A.
 2. Check call logs.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Only calls involving User A should display. No other users' call history visible.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CALLS_072</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr"/>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>User is not logged in</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify call module not accessible without authentication</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Try to access call logs without logging in.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Should redirect to login. No call data exposed.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CALLS_073</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Call Module</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify call behavior when switching between WiFi and cellular</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Start a call on WiFi.
 2. Switch to cellular mid-call.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Call should continue with brief interruption or seamless handoff.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CALLS_074</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr"/>
-      <c r="C75" s="2" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify call with very long duration (1+ hour)</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Maintain a call for 1+ hour.
 2. End call.
 3. Check log.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Call should remain stable. Log should show correct duration.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CALLS_075</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify multiple simultaneous group calls</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Have two different groups initiate calls at the same time.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>User should receive both notifications. Can join one at a time.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CALLS_076</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr"/>
-      <c r="C77" s="2" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify call log with 1000+ entries</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Have 1000+ call log entries.
 2. Open call logs.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Logs should load with pagination. No performance issues.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CALLS_077</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify call when microphone permission is denied</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Deny microphone permission.
 2. Try to make an audio call.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Should show permission request or error message. Call should not proceed without mic.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>CALLS_078</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr"/>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify video call when camera permission is denied</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Deny camera permission.
 2. Try to make a video call.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Should show permission request or fall back to audio-only call.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CALLS_079</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: Call Module</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify call log with exactly 0 entries</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login with new account.
 2. Open call logs.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Empty state should display with appropriate message.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CALLS_080</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr"/>
-      <c r="C81" s="2" t="inlineStr"/>
-      <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify call log with exactly 1 entry</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Make one call.
 2. Open call logs.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Single call log should display correctly with all details.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CALLS_081</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify call duration of 0 seconds (immediate hang up)</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Call and immediately hang up.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Call should log as missed or with 0:00 duration.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CALLS_082</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr"/>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify group call with maximum participants</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Start a group call with maximum allowed participants.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>All participants should connect. Audio/video should work for all.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CALLS_083</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Call Types</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify one-on-one audio call</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Make an audio call to a single user.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Audio call should connect with clear audio both ways.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CALLS_084</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify one-on-one video call</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Make a video call to a single user.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Video call should connect with video and audio both ways.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CALLS_085</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" s="2" t="inlineStr"/>
-      <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify group audio call</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Make an audio call in a group.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>All participants should hear each other.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CALLS_086</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr"/>
-      <c r="C87" s="2" t="inlineStr"/>
-      <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify group video call</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Make a video call in a group.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>All participants should see and hear each other. Grid/tile layout should adjust.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CALLS_087</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr"/>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Call Log Types</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify outgoing call log display</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Make an outgoing call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Should show outgoing call icon, contact name, duration, and timestamp.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>CALLS_088</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr"/>
-      <c r="C89" s="2" t="inlineStr"/>
-      <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify incoming call log display</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Receive and answer an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Should show incoming call icon, caller name, duration, and timestamp.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>CALLS_089</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify missed call log display</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Miss an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Should show missed call icon (red), caller name, and timestamp. No duration.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>CALLS_090</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr"/>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify rejected call log display</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Reject an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Should show rejected/missed call entry with appropriate icon.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C15:C20"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C2:C10"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D25:D30"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="B2:B10"/>
-    <mergeCell ref="D2:D10"/>
-    <mergeCell ref="D40:D41"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Call_Module/Calls_Module_Test_Cases.xlsx
+++ b/Call_Module/Calls_Module_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -794,272 +794,228 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>CALLS_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Verify Call Logs display</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no call history exists</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify empty call logs state</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab with no call history.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No call history").</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>CALLS_011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>User is logged in, caller has very long name</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify handling of very long caller names</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Find caller with very long name.
 3. Observe display.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>CALLS_012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Verify Call Logs scrolling</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>User is logged in, multiple call logs exist</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify call logs scrolling functionality</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>List should scroll smoothly; call entries should remain properly formatted.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>CALLS_013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Verify Call Logs sorting</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>User is logged in with multiple calls</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify calls sorted by most recent first</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe call order.
 3. Verify chronological sorting.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Most recent calls should appear at the top; older calls below.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>CALLS_014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Verify Call Details panel</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>User is logged in and call log is selected</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify Call Details header display</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log entry.
 3. Observe right panel header.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>"Call Details" header should display at top of right panel.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Verify caller info in Call Details</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Observe caller info section.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Caller profile picture, name, and online status (e.g., "Offline") should display.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_016</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Verify call type display (Missed Call)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Calls tab.
-2. Click on missed call entry.
-3. Observe call type.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>"Missed Call" label with red indicator and timestamp should display.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1071,7 +1027,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CALLS_017</t>
+          <t>CALLS_015</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1079,31 +1035,31 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify call duration display</t>
+          <t>Verify caller info in Call Details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe duration.</t>
+3. Observe caller info section.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Call duration should display (e.g., "00:00" for missed calls, "0s" for brief calls).</t>
+          <t>Caller profile picture, name, and online status (e.g., "Offline") should display.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CALLS_018</t>
+          <t>CALLS_016</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -1111,19 +1067,19 @@
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify voice call button in Call Details</t>
+          <t>Verify call type display (Missed Call)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Observe action buttons.</t>
+2. Click on missed call entry.
+3. Observe call type.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Voice call button (phone icon) should be visible and clickable.</t>
+          <t>"Missed Call" label with red indicator and timestamp should display.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1135,7 +1091,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CALLS_019</t>
+          <t>CALLS_017</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -1143,63 +1099,51 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify video call button in Call Details</t>
+          <t>Verify call duration display</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on any call log.
+3. Observe duration.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Call duration should display (e.g., "00:00" for missed calls, "0s" for brief calls).</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_018</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Verify voice call button in Call Details</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe action buttons.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Video call button (camera icon) should be visible and clickable.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Verify Call Details tabs</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and call log is selected</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Verify Participants tab display</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Observe tabs section.</t>
-        </is>
-      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>"Participants" tab should be visible and selected by default (purple underline).</t>
+          <t>Voice call button (phone icon) should be visible and clickable.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1211,7 +1155,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CALLS_021</t>
+          <t>CALLS_019</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -1219,63 +1163,75 @@
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify Recording tab display</t>
+          <t>Verify video call button in Call Details</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on any call log.
+3. Observe action buttons.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Video call button (camera icon) should be visible and clickable.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_020</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Verify Call Details tabs</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and call log is selected</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Verify Participants tab display</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>"Recording" tab should be visible and clickable.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify History tab display</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Observe tabs section.</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>"History" tab should be visible and clickable.</t>
+          <t>"Participants" tab should be visible and selected by default (purple underline).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CALLS_023</t>
+          <t>CALLS_021</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1283,75 +1239,63 @@
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify tab switching functionality</t>
+          <t>Verify Recording tab display</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Click on different tabs.</t>
+3. Observe tabs section.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tabs should switch smoothly; selected tab should show purple underline.</t>
+          <t>"Recording" tab should be visible and clickable.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CALLS_024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Verify Participants tab</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Participants tab is active</t>
-        </is>
-      </c>
+          <t>CALLS_022</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify participants list display</t>
+          <t>Verify History tab display</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. View Participants tab.</t>
+3. Observe tabs section.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>List of call participants should display with profile pictures, names, and timestamps.</t>
+          <t>"History" tab should be visible and clickable.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CALLS_025</t>
+          <t>CALLS_023</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1359,63 +1303,75 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify participant profile picture</t>
+          <t>Verify tab switching functionality</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe participant avatars.</t>
+3. Click on different tabs.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Each participant should show profile picture or default avatar.</t>
+          <t>Tabs should switch smoothly; selected tab should show purple underline.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CALLS_026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
+          <t>CALLS_024</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Verify Participants tab</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Participants tab is active</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify participant name display</t>
+          <t>Verify participants list display</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe participant names.</t>
+3. View Participants tab.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Participant names should display in "First Name Last Name" format.</t>
+          <t>List of call participants should display with profile pictures, names, and timestamps.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CALLS_027</t>
+          <t>CALLS_025</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -1423,19 +1379,19 @@
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify participant join timestamp</t>
+          <t>Verify participant profile picture</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe timestamps.</t>
+3. Observe participant avatars.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Join timestamp should display below each participant name (e.g., "05 Feb, 10:53 AM").</t>
+          <t>Each participant should show profile picture or default avatar.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1447,7 +1403,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CALLS_028</t>
+          <t>CALLS_026</t>
         </is>
       </c>
       <c r="B29" s="2" t="n"/>
@@ -1455,19 +1411,19 @@
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify participant call duration</t>
+          <t>Verify participant name display</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe duration on right.</t>
+3. Observe participant names.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Individual participant duration should display on right side (e.g., "0s").</t>
+          <t>Participant names should display in "First Name Last Name" format.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1479,7 +1435,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CALLS_029</t>
+          <t>CALLS_027</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -1487,589 +1443,407 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>Verify participant join timestamp</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on any call log.
+3. Observe timestamps.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Join timestamp should display below each participant name (e.g., "05 Feb, 10:53 AM").</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_028</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Verify participant call duration</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on any call log.
+3. Observe duration on right.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Individual participant duration should display on right side (e.g., "0s").</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_029</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>Verify multiple participants display</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on group call log.
 3. Observe participants list.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>All participants should be listed separately with their individual details.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>CALLS_030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Verify Participants tab</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>User is logged in, call has no other participants</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Verify single participant display</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on one-on-one call.
 3. View Participants tab.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Only the other participant should display; appropriate message if no participants.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>CALLS_031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Verify Recording tab</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>User is logged in and Recording tab is active</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Verify Recording tab content display</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click on Recording tab.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Recording tab should display recordings if available or empty state message.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>CALLS_032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Verify Recording tab</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no recordings exist</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Verify empty Recording tab state</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on call without recording.
 3. Click Recording tab.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No recordings available").</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>CALLS_033</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Verify History tab</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>User is logged in and History tab is active</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Verify History tab content display</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click on History tab.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Call history with the selected user should display.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>CALLS_034</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Verify History tab</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no previous calls with user</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Verify empty History tab state</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on first-time call.
 3. Click History tab.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Empty state or only current call should display.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>CALLS_035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Verify call initiation from Call Details</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>User is logged in and Call Details is open</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Verify voice call initiation from details</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click voice call button.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Voice call should be initiated; calling screen should appear.</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_036</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Verify video call initiation from details</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Click video call button.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Video call should be initiated; video calling screen should appear.</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_037</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Verify Calls module on desktop browser</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1. Open application on desktop.
-2. Navigate to Calls tab.
-3. Resize browser window.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Layout should adjust dynamically; call logs and details panel should remain functional.</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_038</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Verify Calls module on mobile device</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1. Open application on mobile browser/device.
-2. Navigate to Calls tab.
-3. Check layout.</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Call logs should fit screen properly; details may show on separate screen.</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_039</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Verify Calls tab highlight in navigation</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on Calls tab in bottom navigation.
-2. Observe tab appearance.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Calls tab should be highlighted/selected (purple icon).</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_040</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation between tabs</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on Calls tab.
-2. Click on Chats tab.
-3. Click back on Calls tab.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Navigation should work smoothly; Call logs should reload correctly.</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_041</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Verify Call Logs loading</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, slow network</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Verify loading state during slow connection</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1. Simulate slow network.
-2. Navigate to Calls tab.
-3. Observe loading behavior.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Loading indicator should display while call logs are being fetched.</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_042</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Verify error handling on network failure</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Navigate to Calls tab.
-3. Observe error handling.</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Appropriate error message should display with retry option.</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_043</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Verify Audio Call</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on a conversation</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Verify initiating an audio call</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a one-on-one conversation.
-2. Click the audio call (phone) icon in header.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Audio call should initiate. Calling screen should appear with user name, avatar, and call controls.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2081,7 +1855,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CALLS_044</t>
+          <t>CALLS_036</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -2089,17 +1863,19 @@
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call ringing state</t>
+          <t>Verify video call initiation from details</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Initiate an audio call to another user.</t>
+          <t>1. Navigate to Calls tab.
+2. Click on any call log.
+3. Click video call button.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Ringing state should display with 'Calling...' or ringing indicator. Ring tone should play.</t>
+          <t>Video call should be initiated; video calling screen should appear.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2111,38 +1887,51 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CALLS_045</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
+          <t>CALLS_037</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call connected state</t>
+          <t>Verify Calls module on desktop browser</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Initiate audio call.
-2. Other user accepts.</t>
+          <t>1. Open application on desktop.
+2. Navigate to Calls tab.
+3. Resize browser window.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Call should connect. Timer should start. Audio should be active both ways.</t>
+          <t>Layout should adjust dynamically; call logs and details panel should remain functional.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CALLS_046</t>
+          <t>CALLS_038</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -2150,62 +1939,74 @@
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call mute/unmute</t>
+          <t>Verify Calls module on mobile device</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. During an active audio call.
-2. Click mute button.
-3. Click unmute.</t>
+          <t>1. Open application on mobile browser/device.
+2. Navigate to Calls tab.
+3. Check layout.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Mute should silence outgoing audio. Unmute should restore it. Icon should toggle.</t>
+          <t>Call logs should fit screen properly; details may show on separate screen.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CALLS_047</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
+          <t>CALLS_039</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Verify navigation</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call speaker toggle</t>
+          <t>Verify Calls tab highlight in navigation</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. During an active audio call.
-2. Click speaker button.</t>
+          <t>1. Click on Calls tab in bottom navigation.
+2. Observe tab appearance.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Audio should switch between earpiece and speaker. Icon should toggle.</t>
+          <t>Calls tab should be highlighted/selected (purple icon).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CALLS_048</t>
+          <t>CALLS_040</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -2213,61 +2014,41 @@
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify ending an audio call</t>
+          <t>Verify navigation between tabs</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. During an active audio call.
-2. Click end call (red) button.</t>
+          <t>1. Click on Calls tab.
+2. Click on Chats tab.
+3. Click back on Calls tab.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Call should end. Both users should return to chat. Call duration should log.</t>
+          <t>Navigation should work smoothly; Call logs should reload correctly.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_049</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call in group</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a group conversation.
-2. Initiate an audio call.</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Group audio call should initiate. All members should receive call notification.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>CALLS_050</t>
+          <t>CALLS_041</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2277,62 +2058,65 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Verify Audio Call</t>
+          <t>Verify Call Logs loading</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is logged in, slow network</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call when user is offline</t>
+          <t>Verify loading state during slow connection</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1. Try to audio call a user who is offline.</t>
+          <t>1. Simulate slow network.
+2. Navigate to Calls tab.
+3. Observe loading behavior.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Call should ring and eventually show 'User unavailable' or similar message.</t>
+          <t>Loading indicator should display while call logs are being fetched.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>CALLS_051</t>
+          <t>CALLS_042</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, network disconnected</t>
+          <t>User is logged in, network error</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call fails without network</t>
+          <t>Verify error handling on network failure</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
-2. Try to initiate an audio call.</t>
+2. Navigate to Calls tab.
+3. Observe error handling.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Error message should display indicating no network connection.</t>
+          <t>Appropriate error message should display with retry option.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2342,44 +2126,19 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_052</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="n"/>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on an active call</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call drops on network loss</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>1. Be on an active audio call.
-2. Disconnect network.</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Call should drop with reconnecting attempt or error message.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>CALLS_053</t>
+          <t>CALLS_043</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2389,27 +2148,28 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Verify Incoming Call</t>
+          <t>Verify Audio Call</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and app is open</t>
+          <t>User is logged in and on a conversation</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify incoming audio call notification</t>
+          <t>Verify initiating an audio call</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1. Another user initiates an audio call to you.</t>
+          <t>1. Open a one-on-one conversation.
+2. Click the audio call (phone) icon in header.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
+          <t>Audio call should initiate. Calling screen should appear with user name, avatar, and call controls.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2421,7 +2181,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CALLS_054</t>
+          <t>CALLS_044</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -2429,17 +2189,17 @@
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify incoming video call notification</t>
+          <t>Verify audio call ringing state</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1. Another user initiates a video call to you.</t>
+          <t>1. Initiate an audio call to another user.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
+          <t>Ringing state should display with 'Calling...' or ringing indicator. Ring tone should play.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2451,7 +2211,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>CALLS_055</t>
+          <t>CALLS_045</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -2459,18 +2219,18 @@
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify accepting an incoming audio call</t>
+          <t>Verify audio call connected state</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Receive an incoming audio call.
-2. Click accept/answer button.</t>
+          <t>1. Initiate audio call.
+2. Other user accepts.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Audio call should connect. Call screen should show with active call controls.</t>
+          <t>Call should connect. Timer should start. Audio should be active both ways.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2482,7 +2242,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>CALLS_056</t>
+          <t>CALLS_046</t>
         </is>
       </c>
       <c r="B57" s="2" t="n"/>
@@ -2490,18 +2250,19 @@
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify accepting an incoming video call</t>
+          <t>Verify audio call mute/unmute</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1. Receive an incoming video call.
-2. Click accept/answer button.</t>
+          <t>1. During an active audio call.
+2. Click mute button.
+3. Click unmute.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Video call should connect with both video feeds visible.</t>
+          <t>Mute should silence outgoing audio. Unmute should restore it. Icon should toggle.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2513,7 +2274,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CALLS_057</t>
+          <t>CALLS_047</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -2521,30 +2282,30 @@
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify rejecting an incoming call</t>
+          <t>Verify audio call speaker toggle</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1. Receive an incoming call.
-2. Click reject/decline button.</t>
+          <t>1. During an active audio call.
+2. Click speaker button.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Call should be rejected. Caller should see 'Call declined' or similar. Call logged as missed.</t>
+          <t>Audio should switch between earpiece and speaker. Icon should toggle.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>CALLS_058</t>
+          <t>CALLS_048</t>
         </is>
       </c>
       <c r="B59" s="2" t="n"/>
@@ -2552,18 +2313,18 @@
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify incoming call when app is in background</t>
+          <t>Verify ending an audio call</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1. Minimize the app.
-2. Another user calls you.</t>
+          <t>1. During an active audio call.
+2. Click end call (red) button.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Push notification or system call UI should appear allowing accept/reject.</t>
+          <t>Call should end. Both users should return to chat. Call duration should log.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2575,7 +2336,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CALLS_059</t>
+          <t>CALLS_049</t>
         </is>
       </c>
       <c r="B60" s="2" t="n"/>
@@ -2583,17 +2344,18 @@
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify incoming group call notification</t>
+          <t>Verify audio call in group</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1. A group member initiates a group call.</t>
+          <t>1. Open a group conversation.
+2. Initiate an audio call.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Incoming group call notification should appear with group name and accept/reject options.</t>
+          <t>Group audio call should initiate. All members should receive call notification.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2603,40 +2365,19 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_060</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Verify missed call when not answered</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive an incoming call.
-2. Do not answer until it times out.</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Call should be logged as 'Missed' in call logs. Missed call notification should appear.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CALLS_061</t>
+          <t>CALLS_050</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2646,66 +2387,455 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Verify Incoming Call</t>
+          <t>Verify Audio Call</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>User is logged in with Do Not Disturb enabled</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify incoming call behavior with DND</t>
+          <t>Verify audio call when user is offline</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1. Enable Do Not Disturb.
-2. Receive an incoming call.</t>
+          <t>1. Try to audio call a user who is offline.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Call should be silenced or blocked based on DND settings. Call logged as missed.</t>
+          <t>Call should ring and eventually show 'User unavailable' or similar message.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>CALLS_062</t>
+          <t>CALLS_051</t>
         </is>
       </c>
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call fails without network</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to initiate an audio call.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display indicating no network connection.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_052</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on an active call</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call drops on network loss</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Be on an active audio call.
+2. Disconnect network.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Call should drop with reconnecting attempt or error message.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_053</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Verify Incoming Call</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and app is open</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming audio call notification</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Another user initiates an audio call to you.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_054</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming video call notification</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Another user initiates a video call to you.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_055</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Verify accepting an incoming audio call</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming audio call.
+2. Click accept/answer button.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Audio call should connect. Call screen should show with active call controls.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_056</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Verify accepting an incoming video call</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming video call.
+2. Click accept/answer button.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Video call should connect with both video feeds visible.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_057</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Verify rejecting an incoming call</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming call.
+2. Click reject/decline button.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Call should be rejected. Caller should see 'Call declined' or similar. Call logged as missed.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_058</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming call when app is in background</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Minimize the app.
+2. Another user calls you.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Push notification or system call UI should appear allowing accept/reject.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_059</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming group call notification</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. A group member initiates a group call.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Incoming group call notification should appear with group name and accept/reject options.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_060</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Verify missed call when not answered</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming call.
+2. Do not answer until it times out.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Call should be logged as 'Missed' in call logs. Missed call notification should appear.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_061</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Verify Incoming Call</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with Do Not Disturb enabled</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming call behavior with DND</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Enable Do Not Disturb.
+2. Receive an incoming call.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Call should be silenced or blocked based on DND settings. Call logged as missed.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_062</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
           <t>User is logged in and already on a call</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Verify incoming call while on another call</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Be on an active call.
 2. Receive another incoming call.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>Second call notification should appear with option to accept (end current) or reject.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -3286,7 +3416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3478,66 +3608,76 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_077</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify call when microphone permission is denied</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. Deny microphone permission.
-2. Try to make an audio call.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Should show permission request or error message. Call should not proceed without mic.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CALLS_078</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
+          <t>CALLS_077</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Verify call when microphone permission is denied</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Deny microphone permission.
+2. Try to make an audio call.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Should show permission request or error message. Call should not proceed without mic.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_078</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Verify video call when camera permission is denied</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Deny camera permission.
 2. Try to make a video call.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Should show permission request or fall back to audio-only call.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/Call_Module/Calls_Module_Test_Cases.xlsx
+++ b/Call_Module/Calls_Module_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -794,228 +794,257 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_012</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Verify Call Logs scrolling</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, multiple call logs exist</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify call logs scrolling functionality</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Scroll down through the list.
+3. Scroll back up.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>List should scroll smoothly; call entries should remain properly formatted.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CALLS_010</t>
+          <t>CALLS_013</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Verify Call Logs display</t>
+          <t>Verify Call Logs sorting</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, no call history exists</t>
+          <t>User is logged in with multiple calls</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify empty call logs state</t>
+          <t>Verify calls sorted by most recent first</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Calls tab with no call history.
-2. Observe display.</t>
+          <t>1. Navigate to Calls tab.
+2. Observe call order.
+3. Verify chronological sorting.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Empty state message should display (e.g., "No call history").</t>
+          <t>Most recent calls should appear at the top; older calls below.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CALLS_011</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
+          <t>CALLS_014</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Verify Call Details panel</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, caller has very long name</t>
+          <t>User is logged in and call log is selected</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify handling of very long caller names</t>
+          <t>Verify Call Details header display</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
-2. Find caller with very long name.
-3. Observe display.</t>
+2. Click on any call log entry.
+3. Observe right panel header.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
+          <t>"Call Details" header should display at top of right panel.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Low / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_015</t>
+        </is>
+      </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify caller info in Call Details</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on any call log.
+3. Observe caller info section.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Caller profile picture, name, and online status (e.g., "Offline") should display.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CALLS_012</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Call Logs scrolling</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, multiple call logs exist</t>
-        </is>
-      </c>
+          <t>CALLS_016</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify call logs scrolling functionality</t>
+          <t>Verify call type display (Missed Call)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
-2. Scroll down through the list.
-3. Scroll back up.</t>
+2. Click on missed call entry.
+3. Observe call type.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>List should scroll smoothly; call entries should remain properly formatted.</t>
+          <t>"Missed Call" label with red indicator and timestamp should display.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CALLS_013</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Verify Call Logs sorting</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with multiple calls</t>
-        </is>
-      </c>
+          <t>CALLS_017</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify calls sorted by most recent first</t>
+          <t>Verify call duration display</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
-2. Observe call order.
-3. Verify chronological sorting.</t>
+2. Click on any call log.
+3. Observe duration.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Most recent calls should appear at the top; older calls below.</t>
+          <t>Call duration should display (e.g., "00:00" for missed calls, "0s" for brief calls).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CALLS_014</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Verify Call Details panel</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and call log is selected</t>
-        </is>
-      </c>
+          <t>CALLS_018</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify Call Details header display</t>
+          <t>Verify voice call button in Call Details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
-2. Click on any call log entry.
-3. Observe right panel header.</t>
+2. Click on any call log.
+3. Observe action buttons.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>"Call Details" header should display at top of right panel.</t>
+          <t>Voice call button (phone icon) should be visible and clickable.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1027,7 +1056,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CALLS_015</t>
+          <t>CALLS_019</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1035,19 +1064,19 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify caller info in Call Details</t>
+          <t>Verify video call button in Call Details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe caller info section.</t>
+3. Observe action buttons.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Caller profile picture, name, and online status (e.g., "Offline") should display.</t>
+          <t>Video call button (camera icon) should be visible and clickable.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1059,27 +1088,39 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CALLS_016</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+          <t>CALLS_020</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Verify Call Details tabs</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and call log is selected</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify call type display (Missed Call)</t>
+          <t>Verify Participants tab display</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
-2. Click on missed call entry.
-3. Observe call type.</t>
+2. Click on any call log.
+3. Observe tabs section.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>"Missed Call" label with red indicator and timestamp should display.</t>
+          <t>"Participants" tab should be visible and selected by default (purple underline).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1091,7 +1132,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CALLS_017</t>
+          <t>CALLS_021</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -1099,31 +1140,31 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify call duration display</t>
+          <t>Verify Recording tab display</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe duration.</t>
+3. Observe tabs section.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Call duration should display (e.g., "00:00" for missed calls, "0s" for brief calls).</t>
+          <t>"Recording" tab should be visible and clickable.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CALLS_018</t>
+          <t>CALLS_022</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1131,31 +1172,31 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify voice call button in Call Details</t>
+          <t>Verify History tab display</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe action buttons.</t>
+3. Observe tabs section.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Voice call button (phone icon) should be visible and clickable.</t>
+          <t>"History" tab should be visible and clickable.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CALLS_019</t>
+          <t>CALLS_023</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -1163,31 +1204,31 @@
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify video call button in Call Details</t>
+          <t>Verify tab switching functionality</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe action buttons.</t>
+3. Click on different tabs.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Video call button (camera icon) should be visible and clickable.</t>
+          <t>Tabs should switch smoothly; selected tab should show purple underline.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CALLS_020</t>
+          <t>CALLS_024</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1197,29 +1238,29 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Verify Call Details tabs</t>
+          <t>Verify Participants tab</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and call log is selected</t>
+          <t>User is logged in and Participants tab is active</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify Participants tab display</t>
+          <t>Verify participants list display</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe tabs section.</t>
+3. View Participants tab.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>"Participants" tab should be visible and selected by default (purple underline).</t>
+          <t>List of call participants should display with profile pictures, names, and timestamps.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1231,7 +1272,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CALLS_021</t>
+          <t>CALLS_025</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1239,19 +1280,19 @@
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify Recording tab display</t>
+          <t>Verify participant profile picture</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe tabs section.</t>
+3. Observe participant avatars.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>"Recording" tab should be visible and clickable.</t>
+          <t>Each participant should show profile picture or default avatar.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1263,7 +1304,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CALLS_022</t>
+          <t>CALLS_026</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -1271,19 +1312,19 @@
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify History tab display</t>
+          <t>Verify participant name display</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe tabs section.</t>
+3. Observe participant names.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>"History" tab should be visible and clickable.</t>
+          <t>Participant names should display in "First Name Last Name" format.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1295,7 +1336,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CALLS_023</t>
+          <t>CALLS_027</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1303,75 +1344,63 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify tab switching functionality</t>
+          <t>Verify participant join timestamp</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Click on different tabs.</t>
+3. Observe timestamps.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Tabs should switch smoothly; selected tab should show purple underline.</t>
+          <t>Join timestamp should display below each participant name (e.g., "05 Feb, 10:53 AM").</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CALLS_024</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Verify Participants tab</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Participants tab is active</t>
-        </is>
-      </c>
+          <t>CALLS_028</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify participants list display</t>
+          <t>Verify participant call duration</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. View Participants tab.</t>
+3. Observe duration on right.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>List of call participants should display with profile pictures, names, and timestamps.</t>
+          <t>Individual participant duration should display on right side (e.g., "0s").</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CALLS_025</t>
+          <t>CALLS_029</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -1379,127 +1408,163 @@
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify participant profile picture</t>
+          <t>Verify multiple participants display</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on group call log.
+3. Observe participants list.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>All participants should be listed separately with their individual details.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_031</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Verify Recording tab</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Recording tab is active</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Verify Recording tab content display</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe participant avatars.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Each participant should show profile picture or default avatar.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+3. Click on Recording tab.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Recording tab should display recordings if available or empty state message.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Verify participant name display</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_033</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Verify History tab</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and History tab is active</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Verify History tab content display</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe participant names.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Participant names should display in "First Name Last Name" format.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+3. Click on History tab.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Call history with the selected user should display.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_027</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Verify participant join timestamp</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_035</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Verify call initiation from Call Details</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Call Details is open</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Verify voice call initiation from details</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
-3. Observe timestamps.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Join timestamp should display below each participant name (e.g., "05 Feb, 10:53 AM").</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_028</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Verify participant call duration</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Observe duration on right.</t>
+3. Click voice call button.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Individual participant duration should display on right side (e.g., "0s").</t>
+          <t>Voice call should be initiated; calling screen should appear.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CALLS_029</t>
+          <t>CALLS_036</t>
         </is>
       </c>
       <c r="B32" s="2" t="n"/>
@@ -1507,311 +1572,411 @@
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple participants display</t>
+          <t>Verify video call initiation from details</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
-2. Click on group call log.
-3. Observe participants list.</t>
+2. Click on any call log.
+3. Click video call button.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>All participants should be listed separately with their individual details.</t>
+          <t>Video call should be initiated; video calling screen should appear.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_037</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verify Calls module on desktop browser</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on desktop.
+2. Navigate to Calls tab.
+3. Resize browser window.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Layout should adjust dynamically; call logs and details panel should remain functional.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>High / Medium</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CALLS_030</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Verify Participants tab</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, call has no other participants</t>
-        </is>
-      </c>
+          <t>CALLS_038</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify single participant display</t>
+          <t>Verify Calls module on mobile device</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Calls tab.
-2. Click on one-on-one call.
-3. View Participants tab.</t>
+          <t>1. Open application on mobile browser/device.
+2. Navigate to Calls tab.
+3. Check layout.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Only the other participant should display; appropriate message if no participants.</t>
+          <t>Call logs should fit screen properly; details may show on separate screen.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_039</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Verify navigation</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Verify Calls tab highlight in navigation</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on Calls tab in bottom navigation.
+2. Observe tab appearance.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Calls tab should be highlighted/selected (purple icon).</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Low</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CALLS_031</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+          <t>CALLS_040</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Verify navigation between tabs</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on Calls tab.
+2. Click on Chats tab.
+3. Click back on Calls tab.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Navigation should work smoothly; Call logs should reload correctly.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_043</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Verify Recording tab</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Recording tab is active</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Verify Recording tab content display</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Click on Recording tab.</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Recording tab should display recordings if available or empty state message.</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Call</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on a conversation</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verify initiating an audio call</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a one-on-one conversation.
+2. Click the audio call (phone) icon in header.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Audio call should initiate. Calling screen should appear with user name, avatar, and call controls.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CALLS_032</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Verify Recording tab</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no recordings exist</t>
-        </is>
-      </c>
+          <t>CALLS_044</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify empty Recording tab state</t>
+          <t>Verify audio call ringing state</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Calls tab.
-2. Click on call without recording.
-3. Click Recording tab.</t>
+          <t>1. Initiate an audio call to another user.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Empty state message should display (e.g., "No recordings available").</t>
+          <t>Ringing state should display with 'Calling...' or ringing indicator. Ring tone should play.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_045</t>
+        </is>
+      </c>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call connected state</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Initiate audio call.
+2. Other user accepts.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Call should connect. Timer should start. Audio should be active both ways.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CALLS_033</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Verify History tab</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and History tab is active</t>
-        </is>
-      </c>
+          <t>CALLS_046</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify History tab content display</t>
+          <t>Verify audio call mute/unmute</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Click on History tab.</t>
+          <t>1. During an active audio call.
+2. Click mute button.
+3. Click unmute.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Call history with the selected user should display.</t>
+          <t>Mute should silence outgoing audio. Unmute should restore it. Icon should toggle.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_047</t>
+        </is>
+      </c>
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call speaker toggle</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. During an active audio call.
+2. Click speaker button.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Audio should switch between earpiece and speaker. Icon should toggle.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CALLS_034</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Verify History tab</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no previous calls with user</t>
-        </is>
-      </c>
+          <t>CALLS_048</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify empty History tab state</t>
+          <t>Verify ending an audio call</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Calls tab.
-2. Click on first-time call.
-3. Click History tab.</t>
+          <t>1. During an active audio call.
+2. Click end call (red) button.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Empty state or only current call should display.</t>
+          <t>Call should end. Both users should return to chat. Call duration should log.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_049</t>
+        </is>
+      </c>
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call in group</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a group conversation.
+2. Initiate an audio call.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Group audio call should initiate. All members should receive call notification.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CALLS_035</t>
+          <t>CALLS_053</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1821,29 +1986,27 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Verify call initiation from Call Details</t>
+          <t>Verify Incoming Call</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and Call Details is open</t>
+          <t>User is logged in and app is open</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify voice call initiation from details</t>
+          <t>Verify incoming audio call notification</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Click voice call button.</t>
+          <t>1. Another user initiates an audio call to you.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Voice call should be initiated; calling screen should appear.</t>
+          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1855,7 +2018,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>CALLS_036</t>
+          <t>CALLS_054</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -1863,19 +2026,17 @@
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify video call initiation from details</t>
+          <t>Verify incoming video call notification</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Calls tab.
-2. Click on any call log.
-3. Click video call button.</t>
+          <t>1. Another user initiates a video call to you.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Video call should be initiated; video calling screen should appear.</t>
+          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1887,51 +2048,38 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CALLS_037</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
+          <t>CALLS_055</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify Calls module on desktop browser</t>
+          <t>Verify accepting an incoming audio call</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on desktop.
-2. Navigate to Calls tab.
-3. Resize browser window.</t>
+          <t>1. Receive an incoming audio call.
+2. Click accept/answer button.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Layout should adjust dynamically; call logs and details panel should remain functional.</t>
+          <t>Audio call should connect. Call screen should show with active call controls.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CALLS_038</t>
+          <t>CALLS_056</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -1939,74 +2087,61 @@
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify Calls module on mobile device</t>
+          <t>Verify accepting an incoming video call</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on mobile browser/device.
-2. Navigate to Calls tab.
-3. Check layout.</t>
+          <t>1. Receive an incoming video call.
+2. Click accept/answer button.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Call logs should fit screen properly; details may show on separate screen.</t>
+          <t>Video call should connect with both video feeds visible.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CALLS_039</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
+          <t>CALLS_057</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify Calls tab highlight in navigation</t>
+          <t>Verify rejecting an incoming call</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. Click on Calls tab in bottom navigation.
-2. Observe tab appearance.</t>
+          <t>1. Receive an incoming call.
+2. Click reject/decline button.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Calls tab should be highlighted/selected (purple icon).</t>
+          <t>Call should be rejected. Caller should see 'Call declined' or similar. Call logged as missed.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Medium / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CALLS_040</t>
+          <t>CALLS_058</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -2014,317 +2149,380 @@
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify navigation between tabs</t>
+          <t>Verify incoming call when app is in background</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Click on Calls tab.
-2. Click on Chats tab.
-3. Click back on Calls tab.</t>
+          <t>1. Minimize the app.
+2. Another user calls you.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Navigation should work smoothly; Call logs should reload correctly.</t>
+          <t>Push notification or system call UI should appear allowing accept/reject.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_059</t>
+        </is>
+      </c>
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify incoming group call notification</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. A group member initiates a group call.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Incoming group call notification should appear with group name and accept/reject options.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>CALLS_060</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify missed call when not answered</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive an incoming call.
+2. Do not answer until it times out.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Call should be logged as 'Missed' in call logs. Missed call notification should appear.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_010</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Verify Call Logs display</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no call history exists</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty call logs state</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab with no call history.
+2. Observe display.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Empty state message should display (e.g., "No call history").</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_011</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, caller has very long name</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify handling of very long caller names</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Find caller with very long name.
+3. Observe display.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_030</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Verify Participants tab</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, call has no other participants</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verify single participant display</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on one-on-one call.
+3. View Participants tab.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Only the other participant should display; appropriate message if no participants.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_032</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Verify Recording tab</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no recordings exist</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty Recording tab state</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on call without recording.
+3. Click Recording tab.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Empty state message should display (e.g., "No recordings available").</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_034</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Verify History tab</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no previous calls with user</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty History tab state</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab.
+2. Click on first-time call.
+3. Click History tab.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Empty state or only current call should display.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>CALLS_041</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Verify Call Logs loading</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Calls tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while call logs are being fetched.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>CALLS_042</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Verify error handling on network failure</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Navigate to Calls tab.
 3. Observe error handling.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Appropriate error message should display with retry option.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_043</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Verify Audio Call</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on a conversation</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Verify initiating an audio call</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a one-on-one conversation.
-2. Click the audio call (phone) icon in header.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Audio call should initiate. Calling screen should appear with user name, avatar, and call controls.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_044</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call ringing state</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Initiate an audio call to another user.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Ringing state should display with 'Calling...' or ringing indicator. Ring tone should play.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_045</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call connected state</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>1. Initiate audio call.
-2. Other user accepts.</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Call should connect. Timer should start. Audio should be active both ways.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_046</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call mute/unmute</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>1. During an active audio call.
-2. Click mute button.
-3. Click unmute.</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Mute should silence outgoing audio. Unmute should restore it. Icon should toggle.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_047</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call speaker toggle</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1. During an active audio call.
-2. Click speaker button.</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Audio should switch between earpiece and speaker. Icon should toggle.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_048</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Verify ending an audio call</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>1. During an active audio call.
-2. Click end call (red) button.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Call should end. Both users should return to chat. Call duration should log.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2336,26 +2534,37 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CALLS_049</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
+          <t>CALLS_050</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Call</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call in group</t>
+          <t>Verify audio call when user is offline</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1. Open a group conversation.
-2. Initiate an audio call.</t>
+          <t>1. Try to audio call a user who is offline.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Group audio call should initiate. All members should receive call notification.</t>
+          <t>Call should ring and eventually show 'User unavailable' or similar message.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2365,49 +2574,67 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_051</t>
+        </is>
+      </c>
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio call fails without network</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to initiate an audio call.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display indicating no network connection.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CALLS_050</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Verify Audio Call</t>
-        </is>
-      </c>
+          <t>CALLS_052</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is logged in and on an active call</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call when user is offline</t>
+          <t>Verify audio call drops on network loss</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1. Try to audio call a user who is offline.</t>
+          <t>1. Be on an active audio call.
+2. Disconnect network.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Call should ring and eventually show 'User unavailable' or similar message.</t>
+          <t>Call should drop with reconnecting attempt or error message.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2419,423 +2646,76 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>CALLS_051</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
+          <t>CALLS_061</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Verify Incoming Call</t>
+        </is>
+      </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, network disconnected</t>
+          <t>User is logged in with Do Not Disturb enabled</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call fails without network</t>
+          <t>Verify incoming call behavior with DND</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to initiate an audio call.</t>
+          <t>1. Enable Do Not Disturb.
+2. Receive an incoming call.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Error message should display indicating no network connection.</t>
+          <t>Call should be silenced or blocked based on DND settings. Call logged as missed.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>CALLS_052</t>
+          <t>CALLS_062</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on an active call</t>
+          <t>User is logged in and already on a call</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify audio call drops on network loss</t>
+          <t>Verify incoming call while on another call</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Be on an active audio call.
-2. Disconnect network.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Call should drop with reconnecting attempt or error message.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_053</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Verify Incoming Call</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and app is open</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Verify incoming audio call notification</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>1. Another user initiates an audio call to you.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_054</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Verify incoming video call notification</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>1. Another user initiates a video call to you.</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_055</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Verify accepting an incoming audio call</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive an incoming audio call.
-2. Click accept/answer button.</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Audio call should connect. Call screen should show with active call controls.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_056</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Verify accepting an incoming video call</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive an incoming video call.
-2. Click accept/answer button.</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Video call should connect with both video feeds visible.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_057</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Verify rejecting an incoming call</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive an incoming call.
-2. Click reject/decline button.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Call should be rejected. Caller should see 'Call declined' or similar. Call logged as missed.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_058</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Verify incoming call when app is in background</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>1. Minimize the app.
-2. Another user calls you.</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Push notification or system call UI should appear allowing accept/reject.</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_059</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Verify incoming group call notification</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>1. A group member initiates a group call.</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Incoming group call notification should appear with group name and accept/reject options.</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_060</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Verify missed call when not answered</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive an incoming call.
-2. Do not answer until it times out.</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Call should be logged as 'Missed' in call logs. Missed call notification should appear.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_061</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Verify Incoming Call</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with Do Not Disturb enabled</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Verify incoming call behavior with DND</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>1. Enable Do Not Disturb.
-2. Receive an incoming call.</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Call should be silenced or blocked based on DND settings. Call logged as missed.</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_062</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n"/>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and already on a call</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Verify incoming call while on another call</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Be on an active call.
 2. Receive another incoming call.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Second call notification should appear with option to accept (end current) or reject.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/Call_Module/Calls_Module_Test_Cases.xlsx
+++ b/Call_Module/Calls_Module_Test_Cases.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,13 +85,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,2281 +465,3127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CALLS_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Verify Call Logs display</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Calls tab</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify call logs list loads correctly</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login to application.
 2. Click on "Calls" tab in bottom navigation.
 3. Observe call logs list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Call logs should display with user names, profile pictures, call timestamps, and call type indicators.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CALLS_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify caller name display</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe caller names in the list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Caller names should display clearly in "First Name Last Name" format.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CALLS_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify caller profile picture display</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe profile pictures next to each call log.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Profile pictures should display correctly; default avatar shown for users without pictures.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CALLS_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify call timestamp display</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe timestamps below each caller name.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Timestamps should display in format "DD Mon, HH:MM AM/PM" (e.g., "05 Feb, 12:01 PM").</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CALLS_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify outgoing call indicator (green arrow)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Find call with green outgoing arrow.
 3. Observe indicator.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Outgoing calls should show green arrow pointing up/right next to timestamp.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CALLS_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify missed call indicator (red)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Find call with red missed indicator.
 3. Observe indicator.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Missed calls should show red arrow/indicator next to timestamp.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CALLS_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify call icon on right side</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe phone icon on right side of each entry.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Phone/call icon should be visible on the right side of each call log entry.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CALLS_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify multiple calls from same user display separately</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe calls from same user (e.g., George Alan).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Each call should display as separate entry with its own timestamp.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CALLS_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Verify selected call log highlight</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log entry.
 3. Observe visual indication.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Selected call log should show visual highlight (background color change).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CALLS_012</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Verify Call Logs scrolling</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>User is logged in, multiple call logs exist</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify call logs scrolling functionality</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>List should scroll smoothly; call entries should remain properly formatted.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>CALLS_013</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Verify Call Logs sorting</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>User is logged in with multiple calls</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Verify calls sorted by most recent first</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe call order.
 3. Verify chronological sorting.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Most recent calls should appear at the top; older calls below.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>CALLS_014</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Verify Call Details panel</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>User is logged in and call log is selected</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify Call Details header display</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log entry.
 3. Observe right panel header.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>"Call Details" header should display at top of right panel.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CALLS_015</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify caller info in Call Details</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe caller info section.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Caller profile picture, name, and online status (e.g., "Offline") should display.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>CALLS_016</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Verify call type display (Missed Call)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on missed call entry.
 3. Observe call type.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>"Missed Call" label with red indicator and timestamp should display.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CALLS_017</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Verify call duration display</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe duration.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Call duration should display (e.g., "00:00" for missed calls, "0s" for brief calls).</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>CALLS_018</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Verify voice call button in Call Details</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe action buttons.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Voice call button (phone icon) should be visible and clickable.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>CALLS_019</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Verify video call button in Call Details</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe action buttons.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Video call button (camera icon) should be visible and clickable.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CALLS_020</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Verify Call Details tabs</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>User is logged in and call log is selected</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Verify Participants tab display</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>"Participants" tab should be visible and selected by default (purple underline).</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CALLS_021</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Verify Recording tab display</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>"Recording" tab should be visible and clickable.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CALLS_022</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Verify History tab display</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>"History" tab should be visible and clickable.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>CALLS_023</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Verify tab switching functionality</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click on different tabs.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Tabs should switch smoothly; selected tab should show purple underline.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>CALLS_024</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Verify Participants tab</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Participants tab is active</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Verify participants list display</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. View Participants tab.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>List of call participants should display with profile pictures, names, and timestamps.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>CALLS_025</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Verify participant profile picture</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe participant avatars.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Each participant should show profile picture or default avatar.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>CALLS_026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Verify participant name display</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe participant names.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Participant names should display in "First Name Last Name" format.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>CALLS_027</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Verify participant join timestamp</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe timestamps.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Join timestamp should display below each participant name (e.g., "05 Feb, 10:53 AM").</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>CALLS_028</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Verify participant call duration</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe duration on right.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Individual participant duration should display on right side (e.g., "0s").</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>CALLS_029</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Verify multiple participants display</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on group call log.
 3. Observe participants list.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>All participants should be listed separately with their individual details.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>CALLS_031</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Verify Recording tab</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Recording tab is active</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Verify Recording tab content display</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click on Recording tab.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Recording tab should display recordings if available or empty state message.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>CALLS_033</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Verify History tab</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>User is logged in and History tab is active</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Verify History tab content display</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click on History tab.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Call history with the selected user should display.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>CALLS_035</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Verify call initiation from Call Details</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Call Details is open</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Verify voice call initiation from details</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click voice call button.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>Voice call should be initiated; calling screen should appear.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>CALLS_036</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Verify video call initiation from details</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click video call button.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Video call should be initiated; video calling screen should appear.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>CALLS_037</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Verify Calls module on desktop browser</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Navigate to Calls tab.
 3. Resize browser window.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Layout should adjust dynamically; call logs and details panel should remain functional.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>CALLS_038</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Verify Calls module on mobile device</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>1. Open application on mobile browser/device.
 2. Navigate to Calls tab.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Call logs should fit screen properly; details may show on separate screen.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>CALLS_039</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Verify navigation</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Verify Calls tab highlight in navigation</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>1. Click on Calls tab in bottom navigation.
 2. Observe tab appearance.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Calls tab should be highlighted/selected (purple icon).</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>CALLS_040</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>1. Click on Calls tab.
 2. Click on Chats tab.
 3. Click back on Calls tab.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Navigation should work smoothly; Call logs should reload correctly.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>CALLS_043</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Verify Audio Call</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on a conversation</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Verify initiating an audio call</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>1. Open a one-on-one conversation.
 2. Click the audio call (phone) icon in header.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>Audio call should initiate. Calling screen should appear with user name, avatar, and call controls.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>CALLS_044</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Verify audio call ringing state</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>1. Initiate an audio call to another user.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Ringing state should display with 'Calling...' or ringing indicator. Ring tone should play.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>CALLS_045</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Verify audio call connected state</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>1. Initiate audio call.
 2. Other user accepts.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Call should connect. Timer should start. Audio should be active both ways.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>CALLS_046</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Verify audio call mute/unmute</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>1. During an active audio call.
 2. Click mute button.
 3. Click unmute.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>Mute should silence outgoing audio. Unmute should restore it. Icon should toggle.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>CALLS_047</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Verify audio call speaker toggle</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>1. During an active audio call.
 2. Click speaker button.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>Audio should switch between earpiece and speaker. Icon should toggle.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>CALLS_048</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Verify ending an audio call</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>1. During an active audio call.
 2. Click end call (red) button.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>Call should end. Both users should return to chat. Call duration should log.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>CALLS_049</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Verify audio call in group</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Initiate an audio call.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>Group audio call should initiate. All members should receive call notification.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>CALLS_053</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Verify Incoming Call</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>User is logged in and app is open</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Verify incoming audio call notification</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>1. Another user initiates an audio call to you.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>CALLS_054</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Verify incoming video call notification</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>1. Another user initiates a video call to you.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>CALLS_055</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Verify accepting an incoming audio call</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>1. Receive an incoming audio call.
 2. Click accept/answer button.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>Audio call should connect. Call screen should show with active call controls.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>CALLS_056</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Verify accepting an incoming video call</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>1. Receive an incoming video call.
 2. Click accept/answer button.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Video call should connect with both video feeds visible.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>CALLS_057</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Verify rejecting an incoming call</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>1. Receive an incoming call.
 2. Click reject/decline button.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>Call should be rejected. Caller should see 'Call declined' or similar. Call logged as missed.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>CALLS_058</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Verify incoming call when app is in background</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>1. Minimize the app.
 2. Another user calls you.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>Push notification or system call UI should appear allowing accept/reject.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>CALLS_059</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Verify incoming group call notification</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>1. A group member initiates a group call.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>Incoming group call notification should appear with group name and accept/reject options.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>CALLS_060</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Verify missed call when not answered</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>1. Receive an incoming call.
 2. Do not answer until it times out.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>Call should be logged as 'Missed' in call logs. Missed call notification should appear.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_010</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Verify Call Logs display</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no call history exists</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty call logs state</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Calls tab with no call history.
-2. Observe display.</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Empty state message should display (e.g., "No call history").</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>CALLS_011</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>User is logged in, caller has very long name</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Verify handling of very long caller names</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Find caller with very long name.
 3. Observe display.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_042</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Verify error handling on network failure</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Navigate to Calls tab.
+3. Observe error handling.</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate error message should display with retry option.</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_051</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Verify audio call fails without network</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to initiate an audio call.</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Error message should display indicating no network connection.</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_052</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in and on an active call</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Verify audio call drops on network loss</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>1. Be on an active audio call.
+2. Disconnect network.</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Call should drop with reconnecting attempt or error message.</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_062</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in and already on a call</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Verify incoming call while on another call</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>1. Be on an active call.
+2. Receive another incoming call.</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Second call notification should appear with option to accept (end current) or reject.</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_091</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing Call - Mute Audio</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Audio/video call in progress</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Verify mute/unmute audio during call</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>1. Join call
+2. Click mute button</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Audio muted, mute icon shown, other participants can't hear</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_092</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing Call - Toggle Camera</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Video call in progress</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Verify camera on/off toggle during call</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>1. Join video call
+2. Click camera toggle</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Camera turned off, placeholder shown to others</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_093</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing Call - Speaker Toggle</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Call in progress</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Verify speaker/earpiece toggle</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>1. During call
+2. Click speaker button</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Audio output switches between speaker and earpiece</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_094</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing Call - Screen Share</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Video call in progress</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Verify screen sharing during call</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>1. During video call
+2. Click screen share</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Screen shared with other participants</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_095</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing Call - Recording</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Call in progress, recording enabled</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Verify call recording functionality</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>1. During call
+2. Click record button</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Call recording starts, indicator shown</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_096</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing Call - End Call</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Call in progress</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Verify ending an ongoing call</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>1. During call
+2. Click end call button</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Call ended for user, returned to chat</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_097</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Ongoing Call - Participant List</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Group call in progress</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Verify viewing participants during call</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>1. During group call
+2. Check participant list</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>List of active participants shown</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_098</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Outgoing Call Screen</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Call initiated</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Verify outgoing call UI displayed</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>1. Initiate audio/video call
+2. Check screen</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Outgoing call screen with user info and cancel button</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_099</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Outgoing Call - Cancel</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Outgoing call ringing</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Verify cancelling outgoing call</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>1. Initiate call
+2. Click cancel before answer</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Call cancelled, returned to chat</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_100</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Outgoing Call - User Info</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Outgoing call screen</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Verify user/group info on outgoing call</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>1. Check outgoing call screen</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Recipient name, avatar, call type shown</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_101</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Call Mode - Default</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Call mode set to default</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Verify default call layout</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1. Start call with default mode</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Default call layout displayed</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_102</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Call Mode - Grid</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Call mode set to grid</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Verify grid call layout</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>1. Start group call with grid mode</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Grid layout with all participants visible</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_103</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Call Mode - Spotlight</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Call mode set to spotlight</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Verify spotlight call layout</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1. Start call with spotlight mode</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Active speaker highlighted in spotlight</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_104</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Call Settings - Audio Only</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Audio call initiated</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Verify audio-only call settings</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1. Start audio call
+2. Check controls</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Only audio controls shown, no camera toggle</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_105</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Call Settings - Video</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Video call initiated</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Verify video call settings</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>1. Start video call
+2. Check controls</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Both audio and video controls shown</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_010</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Verify Call Logs display</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, no call history exists</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty call logs state</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>1. Navigate to Calls tab with no call history.
+2. Observe display.</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Empty state message should display (e.g., "No call history").</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>CALLS_030</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Verify Participants tab</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>User is logged in, call has no other participants</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Verify single participant display</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on one-on-one call.
 3. View Participants tab.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>Only the other participant should display; appropriate message if no participants.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>CALLS_032</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Verify Recording tab</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>User is logged in, no recordings exist</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Verify empty Recording tab state</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on call without recording.
 3. Click Recording tab.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No recordings available").</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>CALLS_034</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Verify History tab</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>User is logged in, no previous calls with user</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Verify empty History tab state</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on first-time call.
 3. Click History tab.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>Empty state or only current call should display.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>CALLS_041</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Verify Call Logs loading</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Calls tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>Loading indicator should display while call logs are being fetched.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_042</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Verify error handling on network failure</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Navigate to Calls tab.
-3. Observe error handling.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Appropriate error message should display with retry option.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_050</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Verify Audio Call</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Verify audio call when user is offline</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to audio call a user who is offline.</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Call should ring and eventually show 'User unavailable' or similar message.</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_050</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_061</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Verify Audio Call</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call when user is offline</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to audio call a user who is offline.</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Call should ring and eventually show 'User unavailable' or similar message.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_051</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call fails without network</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to initiate an audio call.</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display indicating no network connection.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_052</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on an active call</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio call drops on network loss</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>1. Be on an active audio call.
-2. Disconnect network.</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Call should drop with reconnecting attempt or error message.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_061</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Verify Incoming Call</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>User is logged in with Do Not Disturb enabled</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>Verify incoming call behavior with DND</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>1. Enable Do Not Disturb.
 2. Receive an incoming call.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>Call should be silenced or blocked based on DND settings. Call logged as missed.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_062</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and already on a call</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Verify incoming call while on another call</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Be on an active call.
-2. Receive another incoming call.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Second call notification should appear with option to accept (end current) or reject.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_106</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Screen Share - Audio Call</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Audio-only call</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Verify screen share not available in audio call</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>1. During audio call
+2. Check for screen share</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Screen share option not available</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_107</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Camera Toggle - Audio Call</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Audio-only call</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Verify camera toggle not available in audio call</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>1. During audio call
+2. Check for camera toggle</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Camera toggle not visible</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_108</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Call Rejected</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Recipient rejects call</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Verify rejected call handling</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>1. Initiate call
+2. Recipient rejects</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Call ended, 'Call rejected' status shown</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_109</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Call Unanswered</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Recipient doesn't answer</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Verify unanswered call timeout</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>1. Initiate call
+2. Wait for timeout</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Call ends after timeout, 'Unanswered' status</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_110</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Call Busy</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Recipient on another call</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Verify busy status handling</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>1. Call user who is on another call</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>'User busy' status shown</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2729,177 +3597,348 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CALLS_063</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Integration: Call Module with Message List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify call log entry created after completing a call</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Make a call.
 2. End call.
 3. Check call logs.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>New call log entry should appear with correct caller, duration, and timestamp.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CALLS_064</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Integration: Call Module with Conversation List</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify call creates/updates conversation in conversation list</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Make a call to a user.
 2. Check conversation list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Conversation with that user should show call activity (e.g., 'Voice call - 2:30').</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CALLS_065</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Integration: Call Module with Notifications</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify missed call notification</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Call User B.
 2. User B doesn't answer.
 3. Check User B's notifications.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>User B should receive a missed call notification with caller info.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_111</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Call + Message List</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Call ended</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify call action message in chat</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Complete a call
+2. Check message list</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Call summary message shown in chat</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_112</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Call + Notification</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Incoming call</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify incoming call notification</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Receive incoming call</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Incoming call UI with accept/reject shown</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_113</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Screen Share + Recording</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Both active</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify screen share and recording together</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Start screen share
+2. Start recording</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Both features work simultaneously</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_114</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Call + Blocked User</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>User blocked</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot call blocked user</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to call blocked user</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Call not initiated, blocked message shown</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2911,170 +3950,301 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CALLS_066</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Regression: Call Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify call logs persist after app restart</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Make several calls.
 2. Close and reopen app.
 3. Check call logs.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>All call logs should be intact with correct details.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CALLS_067</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify call functionality after network reconnection</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Lose network.
 2. Reconnect.
 3. Make a call.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Call should work normally after network reconnection.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CALLS_068</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify call logs after clearing call history</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Clear call history.
 2. Make a new call.
 3. Check logs.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Only the new call should appear. Old logs should be cleared.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_115</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Mute After Reconnect</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Network reconnected during call</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify mute state persists after reconnect</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Mute during call
+2. Brief disconnect
+3. Reconnect</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Mute state preserved after reconnection</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_116</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Call After Previous End</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Previous call ended</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify new call works after ending previous</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. End call
+2. Start new call</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>New call initiates successfully</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_117</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Recording After Call End</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Call ended during recording</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify recording saved when call ends</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Record call
+2. End call</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Recording saved up to call end point</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3086,201 +4256,286 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FF0000"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_070</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Verify call audio/video stream is encrypted</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. Initiate a call.
+2. Inspect network traffic.</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Media streams should be encrypted (SRTP/DTLS). No plain media in transit.</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_071</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Verify call logs only show user's own calls</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as User A.
+2. Check call logs.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Only calls involving User A should display. No other users' call history visible.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_072</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>User is not logged in</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify call module not accessible without authentication</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to access call logs without logging in.</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Should redirect to login. No call data exposed.</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_118</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Call Auth Token</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Valid session</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify call requires valid authentication</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt call without auth</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Call fails without valid token</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CALLS_069</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Security: Call Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify call cannot be initiated to blocked user</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Block a user.
 2. Try to call that user.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Call should be blocked with appropriate message.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_070</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify call audio/video stream is encrypted</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Initiate a call.
-2. Inspect network traffic.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Media streams should be encrypted (SRTP/DTLS). No plain media in transit.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_071</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify call logs only show user's own calls</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as User A.
-2. Check call logs.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Only calls involving User A should display. No other users' call history visible.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_072</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>User is not logged in</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify call module not accessible without authentication</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to access call logs without logging in.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Should redirect to login. No call data exposed.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_119</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Unauthorized Call Join</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Invalid call session</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot join unauthorized call</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to join call without invitation</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Access denied to call session</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3296,270 +4551,430 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CALLS_073</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Call Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify call behavior when switching between WiFi and cellular</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Start a call on WiFi.
 2. Switch to cellular mid-call.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Call should continue with brief interruption or seamless handoff.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CALLS_074</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify call with very long duration (1+ hour)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Maintain a call for 1+ hour.
 2. End call.
 3. Check log.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Call should remain stable. Log should show correct duration.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CALLS_075</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify multiple simultaneous group calls</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Have two different groups initiate calls at the same time.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>User should receive both notifications. Can join one at a time.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CALLS_076</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify call log with 1000+ entries</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Have 1000+ call log entries.
 2. Open call logs.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Logs should load with pagination. No performance issues.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_078</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify video call when camera permission is denied</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Deny camera permission.
+2. Try to make a video call.</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Should show permission request or fall back to audio-only call.</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_120</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Call with 50 Participants</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Large group call</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify call handles many participants</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Start group call with 50 participants</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Call works with grid/tile layout for all</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_121</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Rapid Mute Toggle</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Quick mute/unmute</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify rapid mute toggle handled</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Rapidly toggle mute 10 times</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Final mute state correctly applied</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_122</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Call During Low Battery</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Device at 5% battery</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify call behavior on low battery</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Start call at low battery</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Call works, battery warning may show</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CALLS_077</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify call when microphone permission is denied</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Deny microphone permission.
 2. Try to make an audio call.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Should show permission request or error message. Call should not proceed without mic.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CALLS_078</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify video call when camera permission is denied</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Deny camera permission.
-2. Try to make a video call.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Should show permission request or fall back to audio-only call.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_123</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Screen Share Permission Denied</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>User denies screen share</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Verify handling of denied screen share permission</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. Click screen share
+2. Deny permission</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate message shown, call continues</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3575,193 +4990,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CALLS_079</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Boundary: Call Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify call log with exactly 0 entries</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login with new account.
 2. Open call logs.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Empty state should display with appropriate message.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CALLS_080</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify call log with exactly 1 entry</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Make one call.
 2. Open call logs.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Single call log should display correctly with all details.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CALLS_081</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify call duration of 0 seconds (immediate hang up)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Call and immediately hang up.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Call should log as missed or with 0:00 duration.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CALLS_082</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify group call with maximum participants</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Start a group call with maximum allowed participants.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>All participants should connect. Audio/video should work for all.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_124</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Call Duration - Short</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1 second call</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify very short call recorded</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Start and immediately end call</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Short call logged in call history</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_125</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Call Duration - Long</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>60+ minute call</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify long call stability</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Maintain call for 60+ minutes</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Call remains stable without degradation</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_126</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Call with 0 Participants</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>All participants leave</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify call ends when empty</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. All participants leave call</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Call session terminated automatically</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3777,318 +5319,529 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CALLS_083</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Call Types</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify one-on-one audio call</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Make an audio call to a single user.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Audio call should connect with clear audio both ways.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CALLS_084</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify one-on-one video call</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Make a video call to a single user.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Video call should connect with video and audio both ways.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CALLS_085</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify group audio call</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Make an audio call in a group.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>All participants should hear each other.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CALLS_086</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify group video call</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Make a video call in a group.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>All participants should see and hear each other. Grid/tile layout should adjust.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CALLS_087</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Call Log Types</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify outgoing call log display</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Make an outgoing call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Should show outgoing call icon, contact name, duration, and timestamp.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CALLS_088</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify incoming call log display</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Receive and answer an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Should show incoming call icon, caller name, duration, and timestamp.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CALLS_089</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify missed call log display</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Miss an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Should show missed call icon (red), caller name, and timestamp. No duration.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CALLS_090</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify rejected call log display</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Reject an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Should show rejected/missed call entry with appropriate icon.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_127</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Audio Call - User</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>1-on-1 audio call</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify audio call to single user</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Start audio call to user</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Audio call connected with user</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_128</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Video Call - User</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1-on-1 video call</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Verify video call to single user</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. Start video call to user</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Video call connected with user</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_129</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Audio Call - Group</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Group audio call</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Verify audio call in group</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. Start audio call in group</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Group audio call with multiple participants</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_130</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Video Call - Group</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Group video call</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Verify video call in group</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. Start video call in group</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Group video call with multiple participants</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>CALLS_131</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Call - Offline User</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Target user offline</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Verify calling offline user</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. Call offline user</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Call rings then shows unanswered/unavailable</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>

--- a/Call_Module/Calls_Module_Test_Cases.xlsx
+++ b/Call_Module/Calls_Module_Test_Cases.xlsx
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -81,11 +81,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +100,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,3069 +529,3680 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>CALLS_001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Verify Call Logs display</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Calls tab</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify call logs list loads correctly</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Login to application.
 2. Click on "Calls" tab in bottom navigation.
 3. Observe call logs list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Call logs should display with user names, profile pictures, call timestamps, and call type indicators.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>CALLS_002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify caller name display</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe caller names in the list.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Caller names should display clearly in "First Name Last Name" format.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CALLS_003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify caller profile picture display</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe profile pictures next to each call log.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Profile pictures should display correctly; default avatar shown for users without pictures.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CALLS_004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify call timestamp display</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe timestamps below each caller name.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Timestamps should display in format "DD Mon, HH:MM AM/PM" (e.g., "05 Feb, 12:01 PM").</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CALLS_005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify outgoing call indicator (green arrow)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Find call with green outgoing arrow.
 3. Observe indicator.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Outgoing calls should show green arrow pointing up/right next to timestamp.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>CALLS_006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify missed call indicator (red)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Find call with red missed indicator.
 3. Observe indicator.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Missed calls should show red arrow/indicator next to timestamp.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>CALLS_007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify call icon on right side</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe phone icon on right side of each entry.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Phone/call icon should be visible on the right side of each call log entry.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>CALLS_008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify multiple calls from same user display separately</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe calls from same user (e.g., George Alan).</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Each call should display as separate entry with its own timestamp.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>CALLS_009</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify selected call log highlight</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log entry.
 3. Observe visual indication.</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Selected call log should show visual highlight (background color change).</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>CALLS_012</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Verify Call Logs scrolling</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>User is logged in, multiple call logs exist</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify call logs scrolling functionality</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>List should scroll smoothly; call entries should remain properly formatted.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>CALLS_013</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Verify Call Logs sorting</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>User is logged in with multiple calls</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify calls sorted by most recent first</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Observe call order.
 3. Verify chronological sorting.</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Most recent calls should appear at the top; older calls below.</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>CALLS_014</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Verify Call Details panel</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>User is logged in and call log is selected</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Verify Call Details header display</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log entry.
 3. Observe right panel header.</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>"Call Details" header should display at top of right panel.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>CALLS_015</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Verify caller info in Call Details</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe caller info section.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Caller profile picture, name, and online status (e.g., "Offline") should display.</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>CALLS_016</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Verify call type display (Missed Call)</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on missed call entry.
 3. Observe call type.</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>"Missed Call" label with red indicator and timestamp should display.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>CALLS_017</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Verify call duration display</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe duration.</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Call duration should display (e.g., "00:00" for missed calls, "0s" for brief calls).</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>CALLS_018</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Verify voice call button in Call Details</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe action buttons.</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Voice call button (phone icon) should be visible and clickable.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>CALLS_019</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Verify video call button in Call Details</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe action buttons.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Video call button (camera icon) should be visible and clickable.</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>CALLS_020</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Verify Call Details tabs</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>User is logged in and call log is selected</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Verify Participants tab display</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>"Participants" tab should be visible and selected by default (purple underline).</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>CALLS_021</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Verify Recording tab display</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>"Recording" tab should be visible and clickable.</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>CALLS_022</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Verify History tab display</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>"History" tab should be visible and clickable.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>CALLS_023</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Verify tab switching functionality</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click on different tabs.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Tabs should switch smoothly; selected tab should show purple underline.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>CALLS_024</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Verify Participants tab</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Participants tab is active</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Verify participants list display</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. View Participants tab.</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>List of call participants should display with profile pictures, names, and timestamps.</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>CALLS_025</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Verify participant profile picture</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe participant avatars.</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Each participant should show profile picture or default avatar.</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>CALLS_026</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Verify participant name display</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe participant names.</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Participant names should display in "First Name Last Name" format.</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>CALLS_027</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Verify participant join timestamp</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe timestamps.</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Join timestamp should display below each participant name (e.g., "05 Feb, 10:53 AM").</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>CALLS_028</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Verify participant call duration</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Observe duration on right.</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Individual participant duration should display on right side (e.g., "0s").</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>CALLS_029</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Verify multiple participants display</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on group call log.
 3. Observe participants list.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>All participants should be listed separately with their individual details.</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>CALLS_031</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Verify Recording tab</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Recording tab is active</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Verify Recording tab content display</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click on Recording tab.</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Recording tab should display recordings if available or empty state message.</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>CALLS_033</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Verify History tab</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>User is logged in and History tab is active</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Verify History tab content display</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click on History tab.</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Call history with the selected user should display.</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>CALLS_035</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Verify call initiation from Call Details</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Call Details is open</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Verify voice call initiation from details</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click voice call button.</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Voice call should be initiated; calling screen should appear.</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>CALLS_036</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Verify video call initiation from details</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on any call log.
 3. Click video call button.</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Video call should be initiated; video calling screen should appear.</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>CALLS_037</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Verify Calls module on desktop browser</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Navigate to Calls tab.
 3. Resize browser window.</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Layout should adjust dynamically; call logs and details panel should remain functional.</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>CALLS_038</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Verify Calls module on mobile device</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>1. Open application on mobile browser/device.
 2. Navigate to Calls tab.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Call logs should fit screen properly; details may show on separate screen.</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>CALLS_039</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Verify navigation</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Verify Calls tab highlight in navigation</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>1. Click on Calls tab in bottom navigation.
 2. Observe tab appearance.</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Calls tab should be highlighted/selected (purple icon).</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>CALLS_040</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>1. Click on Calls tab.
 2. Click on Chats tab.
 3. Click back on Calls tab.</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Navigation should work smoothly; Call logs should reload correctly.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>CALLS_043</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Verify Audio Call</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on a conversation</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Verify initiating an audio call</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>1. Open a one-on-one conversation.
 2. Click the audio call (phone) icon in header.</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Audio call should initiate. Calling screen should appear with user name, avatar, and call controls.</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>CALLS_044</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Verify audio call ringing state</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>1. Initiate an audio call to another user.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Ringing state should display with 'Calling...' or ringing indicator. Ring tone should play.</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>CALLS_045</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Verify audio call connected state</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>1. Initiate audio call.
 2. Other user accepts.</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Call should connect. Timer should start. Audio should be active both ways.</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>CALLS_046</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Verify audio call mute/unmute</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>1. During an active audio call.
 2. Click mute button.
 3. Click unmute.</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Mute should silence outgoing audio. Unmute should restore it. Icon should toggle.</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>CALLS_047</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Verify audio call speaker toggle</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>1. During an active audio call.
 2. Click speaker button.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Audio should switch between earpiece and speaker. Icon should toggle.</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>CALLS_048</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Verify ending an audio call</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>1. During an active audio call.
 2. Click end call (red) button.</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Call should end. Both users should return to chat. Call duration should log.</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>CALLS_049</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Verify audio call in group</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>1. Open a group conversation.
 2. Initiate an audio call.</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Group audio call should initiate. All members should receive call notification.</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>CALLS_053</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Verify Incoming Call</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>User is logged in and app is open</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Verify incoming audio call notification</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>1. Another user initiates an audio call to you.</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>CALLS_054</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Verify incoming video call notification</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>1. Another user initiates a video call to you.</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Incoming call screen should appear with caller name, avatar, accept and reject buttons.</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>CALLS_055</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Verify accepting an incoming audio call</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>1. Receive an incoming audio call.
 2. Click accept/answer button.</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Audio call should connect. Call screen should show with active call controls.</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>CALLS_056</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Verify accepting an incoming video call</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>1. Receive an incoming video call.
 2. Click accept/answer button.</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Video call should connect with both video feeds visible.</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>CALLS_057</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Verify rejecting an incoming call</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>1. Receive an incoming call.
 2. Click reject/decline button.</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Call should be rejected. Caller should see 'Call declined' or similar. Call logged as missed.</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>CALLS_058</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Verify incoming call when app is in background</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>1. Minimize the app.
 2. Another user calls you.</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Push notification or system call UI should appear allowing accept/reject.</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>CALLS_059</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Verify incoming group call notification</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>1. A group member initiates a group call.</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Incoming group call notification should appear with group name and accept/reject options.</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>CALLS_060</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Verify missed call when not answered</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>1. Receive an incoming call.
 2. Do not answer until it times out.</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Call should be logged as 'Missed' in call logs. Missed call notification should appear.</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>CALLS_011</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>User is logged in, caller has very long name</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Verify handling of very long caller names</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Find caller with very long name.
 3. Observe display.</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Long names should be truncated with ellipsis (...) without breaking layout.</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>CALLS_042</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Verify error handling on network failure</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Navigate to Calls tab.
 3. Observe error handling.</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Appropriate error message should display with retry option.</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>CALLS_051</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>Verify audio call fails without network</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to initiate an audio call.</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Error message should display indicating no network connection.</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>CALLS_052</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on an active call</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Verify audio call drops on network loss</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>1. Be on an active audio call.
 2. Disconnect network.</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Call should drop with reconnecting attempt or error message.</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>CALLS_062</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>User is logged in and already on a call</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Verify incoming call while on another call</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>1. Be on an active call.
 2. Receive another incoming call.</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Second call notification should appear with option to accept (end current) or reject.</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>CALLS_091</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Ongoing Call - Mute Audio</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Audio/video call in progress</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Verify mute/unmute audio during call</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>1. Join call
 2. Click mute button</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>Audio muted, mute icon shown, other participants can't hear</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>CALLS_092</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Ongoing Call - Toggle Camera</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Video call in progress</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>Verify camera on/off toggle during call</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>1. Join video call
 2. Click camera toggle</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Camera turned off, placeholder shown to others</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>CALLS_093</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Ongoing Call - Speaker Toggle</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Call in progress</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Verify speaker/earpiece toggle</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>1. During call
 2. Click speaker button</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>Audio output switches between speaker and earpiece</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>CALLS_094</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Ongoing Call - Screen Share</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Video call in progress</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Verify screen sharing during call</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>1. During video call
 2. Click screen share</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Screen shared with other participants</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>CALLS_095</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Ongoing Call - Recording</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Call in progress, recording enabled</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Verify call recording functionality</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>1. During call
 2. Click record button</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>Call recording starts, indicator shown</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>CALLS_096</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Ongoing Call - End Call</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Call in progress</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Verify ending an ongoing call</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>1. During call
 2. Click end call button</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>Call ended for user, returned to chat</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>CALLS_097</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Ongoing Call - Participant List</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Group call in progress</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Verify viewing participants during call</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>1. During group call
 2. Check participant list</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>List of active participants shown</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>CALLS_098</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Outgoing Call Screen</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Call initiated</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Verify outgoing call UI displayed</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>1. Initiate audio/video call
 2. Check screen</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Outgoing call screen with user info and cancel button</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>CALLS_099</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Outgoing Call - Cancel</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Outgoing call ringing</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Verify cancelling outgoing call</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>1. Initiate call
 2. Click cancel before answer</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>Call cancelled, returned to chat</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>CALLS_100</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Outgoing Call - User Info</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Outgoing call screen</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Verify user/group info on outgoing call</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>1. Check outgoing call screen</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Recipient name, avatar, call type shown</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>CALLS_101</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Call Mode - Default</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Call mode set to default</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Verify default call layout</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>1. Start call with default mode</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Default call layout displayed</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>CALLS_102</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Call Mode - Grid</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Call mode set to grid</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>Verify grid call layout</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>1. Start group call with grid mode</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>Grid layout with all participants visible</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>CALLS_103</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Call Mode - Spotlight</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Call mode set to spotlight</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Verify spotlight call layout</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>1. Start call with spotlight mode</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>Active speaker highlighted in spotlight</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>CALLS_104</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Call Settings - Audio Only</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Audio call initiated</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>Verify audio-only call settings</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>1. Start audio call
 2. Check controls</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Only audio controls shown, no camera toggle</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>CALLS_105</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Call Settings - Video</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Video call initiated</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>Verify video call settings</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
         <is>
           <t>1. Start video call
 2. Check controls</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>Both audio and video controls shown</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="72"/>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_132</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Call Details - Open Details View</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Call log selected</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Verify call details view opens</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on a call log entry
+2. Observe view</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Call details view should show: back button, 'Call Details' header, user info, call info</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_133</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - User Info Display</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Call details open</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Verify call user info is displayed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>1. Open call details
+2. Observe user info</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Should show user avatar, name, and online/offline status</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_134</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - User Status Listener</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Call details open</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Verify real-time user status updates</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>1. Open call details
+2. Have the other user go online/offline</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Status text should update in real-time via UserListener</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_135</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - Participants Tab</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Call details open</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Verify Participants tab content</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Participants tab
+2. Observe content</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>List of call participants with name, avatar, and duration</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_136</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - Recording Tab</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Call details open</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Verify Recording tab content</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Recording tab
+2. Observe content</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>List of recordings with ID, timestamp, and download button (or empty state)</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_137</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - History Tab</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Call details open</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Verify History tab content</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>1. Click History tab
+2. Observe content</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Historical calls with status icons, timestamps, and duration</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_138</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - Participants Tab Default</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Call details open</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Verify Participants is default active tab</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>1. Open call details
+2. Observe active tab</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Participants tab should be active by default</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_139</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - Back Button</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Call details open</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Verify back button navigation</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>1. Click back button
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Should return to call logs list, selectedItemCall cleared</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_140</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - Recording Download</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Recording tab, recordings available</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Verify recording download functionality</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>1. Click download button on a recording
+2. Observe download</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Recording should be fetched as blob and downloaded as 'recording.mp4'</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_141</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - History Call Status Icons</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>History tab with various call types</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Verify correct status icons for call types</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>1. Open History tab
+2. Observe different call entries</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Outgoing calls show outgoing icon, incoming show incoming icon, missed show missed icon</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_142</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - History Call Duration</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>History tab with completed calls</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Verify call duration display</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>1. Open History tab
+2. Observe duration column</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Completed calls show duration in h m s format, unanswered show 00:00</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_143</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - Loading Shimmer</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Call details loading</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Verify shimmer loading state</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>1. Open call details
+2. Observe loading state</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Shimmer placeholder should be shown while user data loads</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n"/>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="n"/>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>CALLS_010</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Verify Call Logs display</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no call history exists</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Verify empty call logs state</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab with no call history.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No call history").</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>CALLS_030</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Verify Participants tab</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>User is logged in, call has no other participants</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Verify single participant display</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on one-on-one call.
 3. View Participants tab.</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>Only the other participant should display; appropriate message if no participants.</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>CALLS_032</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Verify Recording tab</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no recordings exist</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Verify empty Recording tab state</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on call without recording.
 3. Click Recording tab.</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No recordings available").</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>CALLS_034</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Verify History tab</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no previous calls with user</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Verify empty History tab state</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Calls tab.
 2. Click on first-time call.
 3. Click History tab.</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Empty state or only current call should display.</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>CALLS_041</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Verify Call Logs loading</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Calls tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while call logs are being fetched.</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>CALLS_050</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Verify Audio Call</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Verify audio call when user is offline</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Try to audio call a user who is offline.</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>Call should ring and eventually show 'User unavailable' or similar message.</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>CALLS_061</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Verify Incoming Call</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>User is logged in with Do Not Disturb enabled</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Verify incoming call behavior with DND</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Enable Do Not Disturb.
 2. Receive an incoming call.</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>Call should be silenced or blocked based on DND settings. Call logged as missed.</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>CALLS_106</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Screen Share - Audio Call</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Audio-only call</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Verify screen share not available in audio call</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. During audio call
 2. Check for screen share</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>Screen share option not available</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>CALLS_107</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Camera Toggle - Audio Call</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Audio-only call</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Verify camera toggle not available in audio call</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. During audio call
 2. Check for camera toggle</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>Camera toggle not visible</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>CALLS_108</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Call Rejected</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Recipient rejects call</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Verify rejected call handling</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Initiate call
 2. Recipient rejects</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>Call ended, 'Call rejected' status shown</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>CALLS_109</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Call Unanswered</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Recipient doesn't answer</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Verify unanswered call timeout</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Initiate call
 2. Wait for timeout</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>Call ends after timeout, 'Unanswered' status</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>CALLS_110</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Call Busy</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Recipient on another call</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Verify busy status handling</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Call user who is on another call</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>'User busy' status shown</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_144</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Call Details - No Recordings</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Recording tab, no recordings</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for no recordings</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Recording tab for call with no recordings
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Empty state with icon and 'No recording available' text</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_145</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Call Details - Blocked User Status Hidden</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Call details for blocked user</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Verify status hidden for blocked user</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1. Open call details for blocked user
+2. Observe status</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Status text should be empty (getUserStatusVisible returns false)</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3598,6 +4217,454 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_063</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Integration: Call Module with Message List</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify call log entry created after completing a call</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Make a call.
+2. End call.
+3. Check call logs.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>New call log entry should appear with correct caller, duration, and timestamp.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_064</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Integration: Call Module with Conversation List</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify call creates/updates conversation in conversation list</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Make a call to a user.
+2. Check conversation list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Conversation with that user should show call activity (e.g., 'Voice call - 2:30').</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_065</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Integration: Call Module with Notifications</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify missed call notification</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Call User B.
+2. User B doesn't answer.
+3. Check User B's notifications.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>User B should receive a missed call notification with caller info.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_111</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Call + Message List</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Call ended</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify call action message in chat</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Complete a call
+2. Check message list</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Call summary message shown in chat</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_112</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Call + Notification</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Incoming call</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify incoming call notification</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Receive incoming call</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Incoming call UI with accept/reject shown</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_113</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Screen Share + Recording</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Both active</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify screen share and recording together</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Start screen share
+2. Start recording</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Both features work simultaneously</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_146</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Call Details - Call Log Request Builder</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>History tab loading</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify call log request builder configuration</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Open History tab
+2. Monitor API calls</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>CallLogRequestBuilder should use limit 30, callCategory 'call', filtered by UID</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_147</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - Auxiliary Header Menu</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Call details open</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify auxiliary header menu integration</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Open call details
+2. Observe trailing view</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>ChatConfigurator.getDataSource().getAuxiliaryHeaderMenu should render for user</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_114</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Call + Blocked User</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>User blocked</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify cannot call blocked user</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to call blocked user</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Call not initiated, blocked message shown</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3657,596 +4724,262 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_063</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_066</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Integration: Call Module with Message List</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Regression: Call Module</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify call log entry created after completing a call</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Make a call.
-2. End call.
-3. Check call logs.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>New call log entry should appear with correct caller, duration, and timestamp.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_064</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Integration: Call Module with Conversation List</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify call creates/updates conversation in conversation list</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Make a call to a user.
-2. Check conversation list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Conversation with that user should show call activity (e.g., 'Voice call - 2:30').</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_065</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Integration: Call Module with Notifications</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify missed call notification</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Call User B.
-2. User B doesn't answer.
-3. Check User B's notifications.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>User B should receive a missed call notification with caller info.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_111</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Call + Message List</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Call ended</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify call action message in chat</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Complete a call
-2. Check message list</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Call summary message shown in chat</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_112</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Call + Notification</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Incoming call</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify incoming call notification</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Receive incoming call</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Incoming call UI with accept/reject shown</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_113</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Screen Share + Recording</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Both active</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify screen share and recording together</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Start screen share
-2. Start recording</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Both features work simultaneously</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_114</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Call + Blocked User</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>User blocked</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify cannot call blocked user</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Try to call blocked user</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Call not initiated, blocked message shown</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00BF8F00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_066</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Regression: Call Module</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify call logs persist after app restart</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Make several calls.
 2. Close and reopen app.
 3. Check call logs.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>All call logs should be intact with correct details.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>CALLS_067</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify call functionality after network reconnection</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Lose network.
 2. Reconnect.
 3. Make a call.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Call should work normally after network reconnection.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CALLS_068</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify call logs after clearing call history</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Clear call history.
 2. Make a new call.
 3. Check logs.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Only the new call should appear. Old logs should be cleared.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CALLS_115</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Mute After Reconnect</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Network reconnected during call</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify mute state persists after reconnect</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Mute during call
 2. Brief disconnect
 3. Reconnect</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Mute state preserved after reconnection</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CALLS_116</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Call After Previous End</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Previous call ended</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify new call works after ending previous</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. End call
 2. Start new call</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>New call initiates successfully</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+    </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>CALLS_117</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Recording After Call End</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Call ended during recording</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify recording saved when call ends</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Record call
 2. End call</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Recording saved up to call end point</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4257,736 +4990,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_070</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify call audio/video stream is encrypted</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Initiate a call.
-2. Inspect network traffic.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Media streams should be encrypted (SRTP/DTLS). No plain media in transit.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_071</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify call logs only show user's own calls</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Login as User A.
-2. Check call logs.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Only calls involving User A should display. No other users' call history visible.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_072</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>User is not logged in</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify call module not accessible without authentication</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Try to access call logs without logging in.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Should redirect to login. No call data exposed.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_118</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Call Auth Token</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Valid session</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify call requires valid authentication</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Attempt call without auth</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Call fails without valid token</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_069</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Security: Call Module</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify call cannot be initiated to blocked user</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Block a user.
-2. Try to call that user.</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Call should be blocked with appropriate message.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_119</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Unauthorized Call Join</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Invalid call session</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify cannot join unauthorized call</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. Try to join call without invitation</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Access denied to call session</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_073</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Edge Case: Call Module</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify call behavior when switching between WiFi and cellular</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Start a call on WiFi.
-2. Switch to cellular mid-call.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Call should continue with brief interruption or seamless handoff.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_074</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify call with very long duration (1+ hour)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Maintain a call for 1+ hour.
-2. End call.
-3. Check log.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Call should remain stable. Log should show correct duration.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_075</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify multiple simultaneous group calls</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Have two different groups initiate calls at the same time.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>User should receive both notifications. Can join one at a time.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_076</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify call log with 1000+ entries</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Have 1000+ call log entries.
-2. Open call logs.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Logs should load with pagination. No performance issues.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_078</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify video call when camera permission is denied</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Deny camera permission.
-2. Try to make a video call.</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Should show permission request or fall back to audio-only call.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_120</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Call with 50 Participants</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Large group call</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify call handles many participants</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Start group call with 50 participants</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Call works with grid/tile layout for all</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_121</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Rapid Mute Toggle</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Quick mute/unmute</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify rapid mute toggle handled</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. Rapidly toggle mute 10 times</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Final mute state correctly applied</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_122</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Call During Low Battery</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Device at 5% battery</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify call behavior on low battery</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Start call at low battery</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Call works, battery warning may show</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_077</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Verify call when microphone permission is denied</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. Deny microphone permission.
-2. Try to make an audio call.</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Should show permission request or error message. Call should not proceed without mic.</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_123</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Screen Share Permission Denied</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>User denies screen share</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Verify handling of denied screen share permission</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. Click screen share
-2. Deny permission</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Appropriate message shown, call continues</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5046,280 +5049,261 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_079</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_070</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify call audio/video stream is encrypted</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Initiate a call.
+2. Inspect network traffic.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Media streams should be encrypted (SRTP/DTLS). No plain media in transit.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_071</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify call logs only show user's own calls</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Login as User A.
+2. Check call logs.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Only calls involving User A should display. No other users' call history visible.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_072</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>User is not logged in</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify call module not accessible without authentication</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Try to access call logs without logging in.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Should redirect to login. No call data exposed.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_118</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Boundary: Call Module</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Call Auth Token</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Valid session</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify call requires valid authentication</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Attempt call without auth</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Call fails without valid token</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_069</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Security: Call Module</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify call log with exactly 0 entries</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Login with new account.
-2. Open call logs.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Empty state should display with appropriate message.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_080</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify call log with exactly 1 entry</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Make one call.
-2. Open call logs.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Single call log should display correctly with all details.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_081</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify call duration of 0 seconds (immediate hang up)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Call and immediately hang up.
-2. Check call log.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Call should log as missed or with 0:00 duration.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_082</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify group call with maximum participants</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Start a group call with maximum allowed participants.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>All participants should connect. Audio/video should work for all.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_124</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Call Duration - Short</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1 second call</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify very short call recorded</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Start and immediately end call</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Short call logged in call history</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_125</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Call Duration - Long</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>60+ minute call</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify long call stability</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Maintain call for 60+ minutes</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Call remains stable without degradation</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify call cannot be initiated to blocked user</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Block a user.
+2. Try to call that user.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Call should be blocked with appropriate message.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_119</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Unauthorized Call Join</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Invalid call session</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify cannot join unauthorized call</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Try to join call without invitation</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Access denied to call session</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CALLS_126</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Call with 0 Participants</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>All participants leave</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify call ends when empty</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. All participants leave call</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Call session terminated automatically</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0000B0F0"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5375,471 +5359,1439 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_073</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Edge Case: Call Module</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify call behavior when switching between WiFi and cellular</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Start a call on WiFi.
+2. Switch to cellular mid-call.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Call should continue with brief interruption or seamless handoff.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_074</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify call with very long duration (1+ hour)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Maintain a call for 1+ hour.
+2. End call.
+3. Check log.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Call should remain stable. Log should show correct duration.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_075</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify multiple simultaneous group calls</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Have two different groups initiate calls at the same time.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>User should receive both notifications. Can join one at a time.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_076</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify call log with 1000+ entries</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Have 1000+ call log entries.
+2. Open call logs.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Logs should load with pagination. No performance issues.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_078</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify video call when camera permission is denied</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Deny camera permission.
+2. Try to make a video call.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Should show permission request or fall back to audio-only call.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_120</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Call with 50 Participants</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Large group call</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify call handles many participants</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Start group call with 50 participants</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Call works with grid/tile layout for all</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_121</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Rapid Mute Toggle</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Quick mute/unmute</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify rapid mute toggle handled</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Rapidly toggle mute 10 times</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Final mute state correctly applied</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_122</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Call During Low Battery</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Device at 5% battery</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify call behavior on low battery</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Start call at low battery</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Call works, battery warning may show</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_148</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Call Details - Scroll Pagination History</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>History tab with many calls</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify infinite scroll in history</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Open History tab
+2. Scroll to bottom
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>More call history should be fetched via fetchNext()</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_077</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Verify call when microphone permission is denied</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>1. Deny microphone permission.
+2. Try to make an audio call.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Should show permission request or error message. Call should not proceed without mic.</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_123</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Screen Share Permission Denied</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>User denies screen share</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify handling of denied screen share permission</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Click screen share
+2. Deny permission</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate message shown, call continues</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_079</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Boundary: Call Module</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify call log with exactly 0 entries</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Login with new account.
+2. Open call logs.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Empty state should display with appropriate message.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_080</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify call log with exactly 1 entry</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Make one call.
+2. Open call logs.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Single call log should display correctly with all details.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_081</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify call duration of 0 seconds (immediate hang up)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Call and immediately hang up.
+2. Check call log.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Call should log as missed or with 0:00 duration.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_082</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify group call with maximum participants</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Start a group call with maximum allowed participants.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>All participants should connect. Audio/video should work for all.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_124</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Call Duration - Short</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>1 second call</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify very short call recorded</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Start and immediately end call</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Short call logged in call history</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_125</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Call Duration - Long</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>60+ minute call</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify long call stability</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Maintain call for 60+ minutes</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Call remains stable without degradation</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_126</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Call with 0 Participants</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>All participants leave</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify call ends when empty</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. All participants leave call</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Call session terminated automatically</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>CALLS_083</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Call Types</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify one-on-one audio call</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Make an audio call to a single user.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Audio call should connect with clear audio both ways.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>CALLS_084</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify one-on-one video call</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Make a video call to a single user.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Video call should connect with video and audio both ways.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CALLS_085</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify group audio call</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Make an audio call in a group.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>All participants should hear each other.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CALLS_086</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify group video call</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Make a video call in a group.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>All participants should see and hear each other. Grid/tile layout should adjust.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CALLS_087</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Call Log Types</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify outgoing call log display</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Make an outgoing call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Should show outgoing call icon, contact name, duration, and timestamp.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>CALLS_088</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify incoming call log display</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Receive and answer an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Should show incoming call icon, caller name, duration, and timestamp.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>CALLS_089</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify missed call log display</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Miss an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Should show missed call icon (red), caller name, and timestamp. No duration.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>CALLS_090</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify rejected call log display</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Reject an incoming call.
 2. Check call log.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Should show rejected/missed call entry with appropriate icon.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>CALLS_127</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Audio Call - User</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>1-on-1 audio call</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify audio call to single user</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Start audio call to user</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Audio call connected with user</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>CALLS_128</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Video Call - User</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>1-on-1 video call</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify video call to single user</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Start video call to user</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Video call connected with user</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>CALLS_129</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Audio Call - Group</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Group audio call</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify audio call in group</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Start audio call in group</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Group audio call with multiple participants</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>CALLS_130</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Video Call - Group</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Group video call</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Verify video call in group</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. Start video call in group</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Group video call with multiple participants</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_149</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Call Details - Outgoing Call Status</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>History with outgoing calls</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify outgoing call status display</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. View call initiated by logged-in user
+2. Observe status</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Should show 'Outgoing Call' with outgoing icon</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>CALLS_150</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Call Details - Incoming Call Status</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>History with incoming calls</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Verify incoming call status display</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1. View call received by logged-in user
+2. Observe status</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Should show 'Incoming Call' with incoming icon</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CALLS_151</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Call Details - Missed Call Status</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>History with missed calls</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify missed call status display</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. View missed/rejected/busy call
+2. Observe status</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Should show 'Missed Call' with missed icon</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>CALLS_131</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Call - Offline User</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Target user offline</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify calling offline user</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Call offline user</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Call rings then shows unanswered/unavailable</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
